--- a/datasets.xlsx
+++ b/datasets.xlsx
@@ -5,17 +5,17 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jhuamanciza\Desktop\Apps\app_seguimiento_insumos\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jhuamanciza\Desktop\Apps\app_gestion_insumos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{12C9926D-B923-43F3-B46E-2F4CA1931876}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B34652CE-518A-4A5A-B1E6-EB3B6B4B148C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-4230" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="db_insumos" sheetId="1" r:id="rId1"/>
     <sheet name="db_ratios_planta_insumo" sheetId="2" r:id="rId2"/>
-    <sheet name="bd_cuota" sheetId="3" r:id="rId3"/>
+    <sheet name="db_cuota" sheetId="3" r:id="rId3"/>
     <sheet name="db_capacidad_instalada" sheetId="4" r:id="rId4"/>
   </sheets>
   <calcPr calcId="162913"/>
@@ -459,7 +459,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{2C03C665-0CE5-4950-B558-45C586062E94}" name="bd_insumos" displayName="bd_insumos" ref="A1:D73" totalsRowShown="0" headerRowDxfId="21" dataDxfId="20" headerRowCellStyle="Normal 2" dataCellStyle="Normal 2">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{2C03C665-0CE5-4950-B558-45C586062E94}" name="db_insumos" displayName="db_insumos" ref="A1:D73" totalsRowShown="0" headerRowDxfId="21" dataDxfId="20" headerRowCellStyle="Normal 2" dataCellStyle="Normal 2">
   <autoFilter ref="A1:D73" xr:uid="{2C03C665-0CE5-4950-B558-45C586062E94}"/>
   <tableColumns count="4">
     <tableColumn id="1" xr3:uid="{263E8336-1D51-4111-9C56-77840C1CE105}" name="id_insumo" dataDxfId="19" dataCellStyle="Normal 2"/>
@@ -484,7 +484,7 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{22937465-9A69-4D88-ABFA-D3A771C272C4}" name="bd_cuota" displayName="bd_cuota" ref="A1:C2" totalsRowShown="0" headerRowDxfId="10" headerRowCellStyle="Normal 2">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{22937465-9A69-4D88-ABFA-D3A771C272C4}" name="db_cuota" displayName="db_cuota" ref="A1:C2" totalsRowShown="0" headerRowDxfId="10" headerRowCellStyle="Normal 2">
   <autoFilter ref="A1:C2" xr:uid="{22937465-9A69-4D88-ABFA-D3A771C272C4}"/>
   <tableColumns count="3">
     <tableColumn id="1" xr3:uid="{00924FDF-43DC-42C1-96FA-66DF0703D727}" name="cuota" dataDxfId="9" dataCellStyle="Normal 2"/>
@@ -776,7 +776,10 @@
   <dimension ref="A1:D73"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="9" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="48" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.85546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="17.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -6291,8 +6294,10 @@
   <dimension ref="A1:E13"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
+    <col min="1" max="1" width="11.28515625" customWidth="1"/>
     <col min="3" max="3" width="20" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="17.42578125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">

--- a/datasets.xlsx
+++ b/datasets.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jhuamanciza\Desktop\Apps\app_gestion_insumos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B34652CE-518A-4A5A-B1E6-EB3B6B4B148C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1CBCEA93-7B54-45CD-83DF-AAC26CF7D145}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-4230" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-4230" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="db_insumos" sheetId="1" r:id="rId1"/>
@@ -18,17 +18,28 @@
     <sheet name="db_cuota" sheetId="3" r:id="rId3"/>
     <sheet name="db_capacidad_instalada" sheetId="4" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="504" uniqueCount="97">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="518" uniqueCount="111">
   <si>
     <t>nombre_insumo</t>
   </si>
@@ -319,6 +330,48 @@
   </si>
   <si>
     <t>TPAC</t>
+  </si>
+  <si>
+    <t>PRESERVANTE MATERI PRIMAIN 20 A:31028016</t>
+  </si>
+  <si>
+    <t>DESINCRUSTANTE NOVA MF 1090</t>
+  </si>
+  <si>
+    <t>COAGULANTE FERROL AL 30 BIGBAG 500KG</t>
+  </si>
+  <si>
+    <t>PRAESTOL DW30 - FLOCULANTE</t>
+  </si>
+  <si>
+    <t>PRAESTOL A 3040 L-LA - FLOCULANTE</t>
+  </si>
+  <si>
+    <t>PRAESTOL DW27 AG - FLOCULANTE</t>
+  </si>
+  <si>
+    <t>SACO HP LAM.S/LOG.NEGRO 71X105CM</t>
+  </si>
+  <si>
+    <t>SACO PP.JUMBO BLANCO C/VALV.DESC.</t>
+  </si>
+  <si>
+    <t>PETROLEO INDUSTRIAL NRO.6</t>
+  </si>
+  <si>
+    <t>PETROLEO DIESEL B5 S50 PD TASA</t>
+  </si>
+  <si>
+    <t>PETROLEO INDUSTRIAL NRO.500</t>
+  </si>
+  <si>
+    <t>PRODUCTO QUIMICO IN-AMIN-SX</t>
+  </si>
+  <si>
+    <t>HISA 109 A</t>
+  </si>
+  <si>
+    <t>HISA 1225 A:</t>
   </si>
 </sst>
 </file>
@@ -360,7 +413,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyAlignment="1">
       <alignment vertical="top"/>
@@ -369,6 +422,12 @@
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
   </cellXfs>
@@ -459,8 +518,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{2C03C665-0CE5-4950-B558-45C586062E94}" name="db_insumos" displayName="db_insumos" ref="A1:D73" totalsRowShown="0" headerRowDxfId="21" dataDxfId="20" headerRowCellStyle="Normal 2" dataCellStyle="Normal 2">
-  <autoFilter ref="A1:D73" xr:uid="{2C03C665-0CE5-4950-B558-45C586062E94}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{2C03C665-0CE5-4950-B558-45C586062E94}" name="db_insumos" displayName="db_insumos" ref="A1:D87" totalsRowShown="0" headerRowDxfId="21" dataDxfId="20" headerRowCellStyle="Normal 2" dataCellStyle="Normal 2">
+  <autoFilter ref="A1:D87" xr:uid="{2C03C665-0CE5-4950-B558-45C586062E94}"/>
   <tableColumns count="4">
     <tableColumn id="1" xr3:uid="{263E8336-1D51-4111-9C56-77840C1CE105}" name="id_insumo" dataDxfId="19" dataCellStyle="Normal 2"/>
     <tableColumn id="2" xr3:uid="{E595EF24-9F84-444B-92B4-6E75A242AB8D}" name="nombre_insumo" dataDxfId="18" dataCellStyle="Normal 2"/>
@@ -773,10 +832,10 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Hoja1"/>
-  <dimension ref="A1:D73"/>
+  <dimension ref="A1:D87"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.28515625" customWidth="1"/>
     <col min="2" max="2" width="48" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="9.85546875" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="17.42578125" bestFit="1" customWidth="1"/>
@@ -1763,6 +1822,174 @@
         <v>20001580</v>
       </c>
       <c r="D73" s="1"/>
+    </row>
+    <row r="74" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A74" s="4">
+        <v>10200189</v>
+      </c>
+      <c r="B74" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="C74" s="4">
+        <v>10200189</v>
+      </c>
+      <c r="D74" s="4"/>
+    </row>
+    <row r="75" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A75">
+        <v>10200227</v>
+      </c>
+      <c r="B75" s="5" t="s">
+        <v>98</v>
+      </c>
+      <c r="C75" s="4">
+        <v>10200227</v>
+      </c>
+      <c r="D75" s="4"/>
+    </row>
+    <row r="76" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A76">
+        <v>10200228</v>
+      </c>
+      <c r="B76" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="C76" s="4">
+        <v>10200228</v>
+      </c>
+      <c r="D76" s="4"/>
+    </row>
+    <row r="77" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A77">
+        <v>10200265</v>
+      </c>
+      <c r="B77" s="5" t="s">
+        <v>100</v>
+      </c>
+      <c r="C77" s="4">
+        <v>10200265</v>
+      </c>
+      <c r="D77" s="4"/>
+    </row>
+    <row r="78" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A78">
+        <v>10200266</v>
+      </c>
+      <c r="B78" s="5" t="s">
+        <v>101</v>
+      </c>
+      <c r="C78" s="4">
+        <v>10200266</v>
+      </c>
+      <c r="D78" s="4"/>
+    </row>
+    <row r="79" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A79">
+        <v>10200267</v>
+      </c>
+      <c r="B79" s="5" t="s">
+        <v>102</v>
+      </c>
+      <c r="C79" s="4">
+        <v>10200267</v>
+      </c>
+      <c r="D79" s="4"/>
+    </row>
+    <row r="80" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A80">
+        <v>20001668</v>
+      </c>
+      <c r="B80" s="5" t="s">
+        <v>103</v>
+      </c>
+      <c r="C80" s="4">
+        <v>20001668</v>
+      </c>
+      <c r="D80" s="4"/>
+    </row>
+    <row r="81" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A81">
+        <v>20001688</v>
+      </c>
+      <c r="B81" s="5" t="s">
+        <v>104</v>
+      </c>
+      <c r="C81" s="4">
+        <v>20001688</v>
+      </c>
+      <c r="D81" s="4"/>
+    </row>
+    <row r="82" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A82">
+        <v>30000517</v>
+      </c>
+      <c r="B82" s="5" t="s">
+        <v>105</v>
+      </c>
+      <c r="C82" s="4">
+        <v>30000517</v>
+      </c>
+      <c r="D82" s="4"/>
+    </row>
+    <row r="83" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A83">
+        <v>30000527</v>
+      </c>
+      <c r="B83" s="5" t="s">
+        <v>106</v>
+      </c>
+      <c r="C83" s="4">
+        <v>30000527</v>
+      </c>
+      <c r="D83" s="4"/>
+    </row>
+    <row r="84" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A84">
+        <v>30000528</v>
+      </c>
+      <c r="B84" s="5" t="s">
+        <v>107</v>
+      </c>
+      <c r="C84" s="4">
+        <v>30000528</v>
+      </c>
+      <c r="D84" s="4"/>
+    </row>
+    <row r="85" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A85">
+        <v>31013555</v>
+      </c>
+      <c r="B85" s="5" t="s">
+        <v>108</v>
+      </c>
+      <c r="C85" s="4">
+        <v>31013555</v>
+      </c>
+      <c r="D85" s="4"/>
+    </row>
+    <row r="86" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A86">
+        <v>31029889</v>
+      </c>
+      <c r="B86" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="C86" s="4">
+        <v>31029889</v>
+      </c>
+      <c r="D86" s="4"/>
+    </row>
+    <row r="87" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A87">
+        <v>31029890</v>
+      </c>
+      <c r="B87" s="5" t="s">
+        <v>110</v>
+      </c>
+      <c r="C87" s="4">
+        <v>31029890</v>
+      </c>
+      <c r="D87" s="4"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1777,6 +2004,9 @@
   <sheetPr codeName="Hoja2"/>
   <dimension ref="A1:C406"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="3" max="3" width="15.7109375" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">

--- a/datasets.xlsx
+++ b/datasets.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jhuamanciza\Desktop\Apps\app_gestion_insumos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1CBCEA93-7B54-45CD-83DF-AAC26CF7D145}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C9A36E4C-FAC7-496C-8D62-F19E5A92D32F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-4230" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-4230" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="db_insumos" sheetId="1" r:id="rId1"/>
@@ -18,7 +18,7 @@
     <sheet name="db_cuota" sheetId="3" r:id="rId3"/>
     <sheet name="db_capacidad_instalada" sheetId="4" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191028"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -39,7 +39,10 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="518" uniqueCount="111">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="920" uniqueCount="120">
+  <si>
+    <t>id_insumo</t>
+  </si>
   <si>
     <t>nombre_insumo</t>
   </si>
@@ -50,6 +53,9 @@
     <t>valor_redondeo</t>
   </si>
   <si>
+    <t>Precio Unitario</t>
+  </si>
+  <si>
     <t>ACIDO NITRICO IND 50-75 CIL 260 KG</t>
   </si>
   <si>
@@ -116,9 +122,6 @@
     <t>KOARET PA 3230 T</t>
   </si>
   <si>
-    <t>LABUFLOC 1650</t>
-  </si>
-  <si>
     <t>MEK ADITIVO TECNICO 5191 - BOT 1 L</t>
   </si>
   <si>
@@ -212,18 +215,12 @@
     <t>SOLVENTE 5661-4 MEK FREE P/CODIF. IMAJE</t>
   </si>
   <si>
-    <t>SACO HP LAM BLANCO S/LOGO 28"X43"</t>
-  </si>
-  <si>
     <t>PROPHORCE SA SPECIAL - TAM-1000-KG</t>
   </si>
   <si>
     <t>ANTIOXIDANTE BHT ADVANCED B30 PLUS AC</t>
   </si>
   <si>
-    <t>HILO - POLIEST COLOR P/COSER SC (08KG)</t>
-  </si>
-  <si>
     <t>TINTA PARA MAQUINA ANSER NP4</t>
   </si>
   <si>
@@ -233,21 +230,12 @@
     <t>HIELO AGUA EN BLOQUE</t>
   </si>
   <si>
-    <t>ACIDO ACETICO GLACIAL 99.85% FOOD GRADE</t>
-  </si>
-  <si>
     <t>ANTIOXIDANTE BHT VITAL-OX-30 CA2</t>
   </si>
   <si>
     <t>CARTUCHO P/CODIF. TINTA ET10 NEGRO</t>
   </si>
   <si>
-    <t>ESLINGA DESECHA 1.5TM 140 X180 X1.50 NAC</t>
-  </si>
-  <si>
-    <t>ESLINGA DESECHA 1.5TM 150 X180 X1.35 NAC</t>
-  </si>
-  <si>
     <t>PROPHORCE AC 600</t>
   </si>
   <si>
@@ -266,7 +254,46 @@
     <t xml:space="preserve">SACO HP TERM BLANCO C/LOGO 71 X 105CM    </t>
   </si>
   <si>
-    <t>id_insumo</t>
+    <t>PRESERVANTE MATERI PRIMAIN 20 A:31028016</t>
+  </si>
+  <si>
+    <t>DESINCRUSTANTE NOVA MF 1090</t>
+  </si>
+  <si>
+    <t>COAGULANTE FERROL AL 30 BIGBAG 500KG</t>
+  </si>
+  <si>
+    <t>PRAESTOL DW30 - FLOCULANTE</t>
+  </si>
+  <si>
+    <t>PRAESTOL A 3040 L-LA - FLOCULANTE</t>
+  </si>
+  <si>
+    <t>PRAESTOL DW27 AG - FLOCULANTE</t>
+  </si>
+  <si>
+    <t>SACO HP LAM.S/LOG.NEGRO 71X105CM</t>
+  </si>
+  <si>
+    <t>SACO PP.JUMBO BLANCO C/VALV.DESC.</t>
+  </si>
+  <si>
+    <t>PETROLEO INDUSTRIAL NRO.6</t>
+  </si>
+  <si>
+    <t>PETROLEO DIESEL B5 S50 PD TASA</t>
+  </si>
+  <si>
+    <t>PETROLEO INDUSTRIAL NRO.500</t>
+  </si>
+  <si>
+    <t>PRODUCTO QUIMICO IN-AMIN-SX</t>
+  </si>
+  <si>
+    <t>HISA 109 A</t>
+  </si>
+  <si>
+    <t>HISA 1225 A:</t>
   </si>
   <si>
     <t>id_localidad</t>
@@ -278,6 +305,42 @@
     <t>TMSU</t>
   </si>
   <si>
+    <t>Antioxidante</t>
+  </si>
+  <si>
+    <t>Sum. Limpieza</t>
+  </si>
+  <si>
+    <t>Embalaje</t>
+  </si>
+  <si>
+    <t>Envase</t>
+  </si>
+  <si>
+    <t>Preservante</t>
+  </si>
+  <si>
+    <t>Trat. Agua Caldero</t>
+  </si>
+  <si>
+    <t>Coagulantes</t>
+  </si>
+  <si>
+    <t>Floculantes</t>
+  </si>
+  <si>
+    <t>Quelantes</t>
+  </si>
+  <si>
+    <t>Aditivo Petróleo</t>
+  </si>
+  <si>
+    <t>Pet. Chata / Pet. Grupos</t>
+  </si>
+  <si>
+    <t>Pet. Industrial</t>
+  </si>
+  <si>
     <t>TCHI</t>
   </si>
   <si>
@@ -332,46 +395,10 @@
     <t>TPAC</t>
   </si>
   <si>
-    <t>PRESERVANTE MATERI PRIMAIN 20 A:31028016</t>
-  </si>
-  <si>
-    <t>DESINCRUSTANTE NOVA MF 1090</t>
-  </si>
-  <si>
-    <t>COAGULANTE FERROL AL 30 BIGBAG 500KG</t>
-  </si>
-  <si>
-    <t>PRAESTOL DW30 - FLOCULANTE</t>
-  </si>
-  <si>
-    <t>PRAESTOL A 3040 L-LA - FLOCULANTE</t>
-  </si>
-  <si>
-    <t>PRAESTOL DW27 AG - FLOCULANTE</t>
-  </si>
-  <si>
-    <t>SACO HP LAM.S/LOG.NEGRO 71X105CM</t>
-  </si>
-  <si>
-    <t>SACO PP.JUMBO BLANCO C/VALV.DESC.</t>
-  </si>
-  <si>
-    <t>PETROLEO INDUSTRIAL NRO.6</t>
-  </si>
-  <si>
-    <t>PETROLEO DIESEL B5 S50 PD TASA</t>
-  </si>
-  <si>
-    <t>PETROLEO INDUSTRIAL NRO.500</t>
-  </si>
-  <si>
-    <t>PRODUCTO QUIMICO IN-AMIN-SX</t>
-  </si>
-  <si>
-    <t>HISA 109 A</t>
-  </si>
-  <si>
-    <t>HISA 1225 A:</t>
+    <t>cobertura_meta</t>
+  </si>
+  <si>
+    <t>familia</t>
   </si>
 </sst>
 </file>
@@ -392,12 +419,18 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -413,7 +446,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyAlignment="1">
       <alignment vertical="top"/>
@@ -424,18 +457,22 @@
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal 2" xfId="1" xr:uid="{1F5AEC9A-AEFF-4CC3-9C56-BFDDC23BA411}"/>
   </cellStyles>
-  <dxfs count="22">
+  <dxfs count="25">
+    <dxf>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
     <dxf>
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
@@ -472,6 +509,13 @@
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <fill>
+        <patternFill>
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
@@ -484,6 +528,19 @@
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
@@ -518,51 +575,54 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{2C03C665-0CE5-4950-B558-45C586062E94}" name="db_insumos" displayName="db_insumos" ref="A1:D87" totalsRowShown="0" headerRowDxfId="21" dataDxfId="20" headerRowCellStyle="Normal 2" dataCellStyle="Normal 2">
-  <autoFilter ref="A1:D87" xr:uid="{2C03C665-0CE5-4950-B558-45C586062E94}"/>
-  <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{263E8336-1D51-4111-9C56-77840C1CE105}" name="id_insumo" dataDxfId="19" dataCellStyle="Normal 2"/>
-    <tableColumn id="2" xr3:uid="{E595EF24-9F84-444B-92B4-6E75A242AB8D}" name="nombre_insumo" dataDxfId="18" dataCellStyle="Normal 2"/>
-    <tableColumn id="3" xr3:uid="{19F47CBA-25E9-41DD-9F39-04A1A166E6D4}" name="id_final" dataDxfId="17" dataCellStyle="Normal 2"/>
-    <tableColumn id="4" xr3:uid="{D298BFBC-AAB8-4D45-A000-A055026AACE7}" name="valor_redondeo" dataDxfId="16" dataCellStyle="Normal 2"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{2C03C665-0CE5-4950-B558-45C586062E94}" name="db_insumos" displayName="db_insumos" ref="A1:E81" totalsRowShown="0" headerRowDxfId="24" dataDxfId="23" headerRowCellStyle="Normal 2" dataCellStyle="Normal 2">
+  <autoFilter ref="A1:E81" xr:uid="{2C03C665-0CE5-4950-B558-45C586062E94}"/>
+  <tableColumns count="5">
+    <tableColumn id="1" xr3:uid="{263E8336-1D51-4111-9C56-77840C1CE105}" name="id_insumo" dataDxfId="22" dataCellStyle="Normal 2"/>
+    <tableColumn id="2" xr3:uid="{E595EF24-9F84-444B-92B4-6E75A242AB8D}" name="nombre_insumo" dataDxfId="21" dataCellStyle="Normal 2"/>
+    <tableColumn id="3" xr3:uid="{19F47CBA-25E9-41DD-9F39-04A1A166E6D4}" name="id_final" dataDxfId="20" dataCellStyle="Normal 2"/>
+    <tableColumn id="4" xr3:uid="{D298BFBC-AAB8-4D45-A000-A055026AACE7}" name="valor_redondeo" dataDxfId="19" dataCellStyle="Normal 2"/>
+    <tableColumn id="5" xr3:uid="{AB7B71FE-EFDC-4D84-8932-7798008683F5}" name="Precio Unitario" dataDxfId="18" dataCellStyle="Normal 2"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{07CBE449-CBEC-4A9B-8D50-10414F47C93E}" name="db_ratios_planta_insumo" displayName="db_ratios_planta_insumo" ref="A1:C406" totalsRowShown="0" headerRowDxfId="15" dataDxfId="14" headerRowCellStyle="Normal 2" dataCellStyle="Normal 2">
-  <autoFilter ref="A1:C406" xr:uid="{07CBE449-CBEC-4A9B-8D50-10414F47C93E}"/>
-  <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{BF5C1D78-FE32-44F1-8E0B-29584F99D973}" name="id_insumo" dataDxfId="13" dataCellStyle="Normal 2"/>
-    <tableColumn id="2" xr3:uid="{07B70E41-C8DB-4B68-94A6-ACBC2ACB880E}" name="id_localidad" dataDxfId="12" dataCellStyle="Normal 2"/>
-    <tableColumn id="3" xr3:uid="{F3C9C4FB-3ED1-4218-9757-447351615555}" name="ratio_nominal" dataDxfId="11" dataCellStyle="Normal 2"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{07CBE449-CBEC-4A9B-8D50-10414F47C93E}" name="db_ratios_planta_insumo" displayName="db_ratios_planta_insumo" ref="A1:D406" totalsRowShown="0" headerRowDxfId="17" dataDxfId="16" headerRowCellStyle="Normal 2" dataCellStyle="Normal 2">
+  <autoFilter ref="A1:D406" xr:uid="{07CBE449-CBEC-4A9B-8D50-10414F47C93E}"/>
+  <tableColumns count="4">
+    <tableColumn id="1" xr3:uid="{BF5C1D78-FE32-44F1-8E0B-29584F99D973}" name="id_insumo" dataDxfId="15" dataCellStyle="Normal 2"/>
+    <tableColumn id="2" xr3:uid="{07B70E41-C8DB-4B68-94A6-ACBC2ACB880E}" name="id_localidad" dataDxfId="14" dataCellStyle="Normal 2"/>
+    <tableColumn id="3" xr3:uid="{F3C9C4FB-3ED1-4218-9757-447351615555}" name="ratio_nominal" dataDxfId="13" dataCellStyle="Normal 2"/>
+    <tableColumn id="4" xr3:uid="{AB821D8B-CF51-49FD-ACA6-3A6BD959334D}" name="familia" dataDxfId="12" dataCellStyle="Normal 2"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{22937465-9A69-4D88-ABFA-D3A771C272C4}" name="db_cuota" displayName="db_cuota" ref="A1:C2" totalsRowShown="0" headerRowDxfId="10" headerRowCellStyle="Normal 2">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{22937465-9A69-4D88-ABFA-D3A771C272C4}" name="db_cuota" displayName="db_cuota" ref="A1:C2" totalsRowShown="0" headerRowDxfId="11" headerRowCellStyle="Normal 2">
   <autoFilter ref="A1:C2" xr:uid="{22937465-9A69-4D88-ABFA-D3A771C272C4}"/>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{00924FDF-43DC-42C1-96FA-66DF0703D727}" name="cuota" dataDxfId="9" dataCellStyle="Normal 2"/>
-    <tableColumn id="2" xr3:uid="{708137E1-16A6-46FD-9369-809C29035B6F}" name="ind_propio" dataDxfId="8" dataCellStyle="Normal 2"/>
-    <tableColumn id="3" xr3:uid="{B8F1B393-295F-4279-8E98-94DB7BACF701}" name="ind_tercero" dataDxfId="7" dataCellStyle="Normal 2"/>
+    <tableColumn id="1" xr3:uid="{00924FDF-43DC-42C1-96FA-66DF0703D727}" name="cuota" dataDxfId="10" dataCellStyle="Normal 2"/>
+    <tableColumn id="2" xr3:uid="{708137E1-16A6-46FD-9369-809C29035B6F}" name="ind_propio" dataDxfId="9" dataCellStyle="Normal 2"/>
+    <tableColumn id="3" xr3:uid="{B8F1B393-295F-4279-8E98-94DB7BACF701}" name="ind_tercero" dataDxfId="8" dataCellStyle="Normal 2"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{4DD44BEC-7676-4FD5-AF5E-E93AE5D0CA6C}" name="db_capacidad_instalada" displayName="db_capacidad_instalada" ref="A1:E13" totalsRowShown="0" headerRowDxfId="6" dataDxfId="5" headerRowCellStyle="Normal 2" dataCellStyle="Normal 2">
-  <autoFilter ref="A1:E13" xr:uid="{4DD44BEC-7676-4FD5-AF5E-E93AE5D0CA6C}"/>
-  <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{A41A569A-A59A-494C-85BB-81AA7435EA8C}" name="id_localidad" dataDxfId="4" dataCellStyle="Normal 2"/>
-    <tableColumn id="2" xr3:uid="{03F4DB6D-9227-4FAB-8CCA-98AFCDD5247E}" name="cip" dataDxfId="3" dataCellStyle="Normal 2"/>
-    <tableColumn id="3" xr3:uid="{521FF6CB-158F-4664-BE50-EF2D3F75D6A9}" name="maxima_descarga" dataDxfId="2" dataCellStyle="Normal 2"/>
-    <tableColumn id="4" xr3:uid="{2CE13923-7F91-4ED8-8A15-E1C5FCE7A9F3}" name="cobertura_ideal" dataDxfId="1" dataCellStyle="Normal 2"/>
-    <tableColumn id="5" xr3:uid="{9995B1B7-731C-49C4-9444-696B2390BFB5}" name="rendimiento" dataDxfId="0" dataCellStyle="Normal 2"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{4DD44BEC-7676-4FD5-AF5E-E93AE5D0CA6C}" name="db_capacidad_instalada" displayName="db_capacidad_instalada" ref="A1:F13" totalsRowShown="0" headerRowDxfId="7" dataDxfId="6" headerRowCellStyle="Normal 2" dataCellStyle="Normal 2">
+  <autoFilter ref="A1:F13" xr:uid="{4DD44BEC-7676-4FD5-AF5E-E93AE5D0CA6C}"/>
+  <tableColumns count="6">
+    <tableColumn id="1" xr3:uid="{A41A569A-A59A-494C-85BB-81AA7435EA8C}" name="id_localidad" dataDxfId="5" dataCellStyle="Normal 2"/>
+    <tableColumn id="2" xr3:uid="{03F4DB6D-9227-4FAB-8CCA-98AFCDD5247E}" name="cip" dataDxfId="4" dataCellStyle="Normal 2"/>
+    <tableColumn id="3" xr3:uid="{521FF6CB-158F-4664-BE50-EF2D3F75D6A9}" name="maxima_descarga" dataDxfId="3" dataCellStyle="Normal 2"/>
+    <tableColumn id="4" xr3:uid="{2CE13923-7F91-4ED8-8A15-E1C5FCE7A9F3}" name="cobertura_ideal" dataDxfId="2" dataCellStyle="Normal 2"/>
+    <tableColumn id="5" xr3:uid="{9995B1B7-731C-49C4-9444-696B2390BFB5}" name="rendimiento" dataDxfId="1" dataCellStyle="Normal 2"/>
+    <tableColumn id="6" xr3:uid="{C4F92249-5F09-4D80-AF56-CAED317970A5}" name="cobertura_meta" dataDxfId="0" dataCellStyle="Normal 2"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -832,35 +892,39 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Hoja1"/>
-  <dimension ref="A1:D87"/>
+  <dimension ref="A1:E81"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12.28515625" customWidth="1"/>
     <col min="2" max="2" width="48" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="9.85546875" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="17.42578125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="16.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+        <v>3</v>
+      </c>
+      <c r="E1" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
         <v>31008221</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C2" s="1">
         <v>31008221</v>
@@ -868,13 +932,16 @@
       <c r="D2" s="1">
         <v>260</v>
       </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E2" s="5">
+        <v>0.82</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" s="1">
         <v>10200008</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C3" s="1">
         <v>10200008</v>
@@ -882,13 +949,16 @@
       <c r="D3" s="1">
         <v>1200</v>
       </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E3" s="5">
+        <v>2.1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
         <v>10200009</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C4" s="1">
         <v>10200009</v>
@@ -896,13 +966,16 @@
       <c r="D4" s="1">
         <v>1260</v>
       </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E4" s="5">
+        <v>2.21</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
         <v>10200012</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C5" s="1">
         <v>10200012</v>
@@ -910,13 +983,16 @@
       <c r="D5" s="1">
         <v>800</v>
       </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E5" s="5">
+        <v>6.3</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
         <v>10200011</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C6" s="1">
         <v>10200011</v>
@@ -924,13 +1000,16 @@
       <c r="D6" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E6" s="5">
+        <v>5.65</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
         <v>10200015</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C7" s="1">
         <v>10200011</v>
@@ -938,13 +1017,16 @@
       <c r="D7" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E7" s="5">
+        <v>4.51</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
         <v>10200021</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C8" s="1">
         <v>10200021</v>
@@ -952,13 +1034,16 @@
       <c r="D8" s="1">
         <v>30000</v>
       </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E8" s="5">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="1">
         <v>10200023</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C9" s="1">
         <v>10200023</v>
@@ -966,13 +1051,16 @@
       <c r="D9" s="1">
         <v>40000</v>
       </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E9" s="5">
+        <v>0.41</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" s="1">
         <v>20000560</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C10" s="1">
         <v>20000560</v>
@@ -980,13 +1068,16 @@
       <c r="D10" s="1">
         <v>640</v>
       </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E10" s="5">
+        <v>3.95</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" s="1">
         <v>10200045</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C11" s="1">
         <v>10200045</v>
@@ -994,13 +1085,16 @@
       <c r="D11" s="1">
         <v>1000</v>
       </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E11" s="5">
+        <v>0.79</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" s="1">
         <v>20000577</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C12" s="1">
         <v>20000579</v>
@@ -1008,13 +1102,16 @@
       <c r="D12" s="1">
         <v>50</v>
       </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E12" s="5">
+        <v>6.8918918918918912</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" s="1">
         <v>20000578</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C13" s="1">
         <v>20000579</v>
@@ -1022,13 +1119,16 @@
       <c r="D13" s="1">
         <v>50</v>
       </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E13" s="5">
+        <v>5.6216216216216219</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" s="1">
         <v>20000579</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C14" s="1">
         <v>20000579</v>
@@ -1036,13 +1136,16 @@
       <c r="D14" s="1">
         <v>50</v>
       </c>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E14" s="5">
+        <v>6.8918918918918912</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" s="1">
         <v>32004434</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C15" s="1">
         <v>32004434</v>
@@ -1050,13 +1153,16 @@
       <c r="D15" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E15" s="5">
+        <v>2.2000000000000002</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" s="1">
         <v>31010971</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="C16" s="1">
         <v>31010971</v>
@@ -1064,13 +1170,16 @@
       <c r="D16" s="1">
         <v>30</v>
       </c>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E16" s="5">
+        <v>5.2</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" s="1">
         <v>31010973</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C17" s="1">
         <v>31010973</v>
@@ -1078,13 +1187,16 @@
       <c r="D17" s="1">
         <v>50</v>
       </c>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E17" s="5">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" s="1">
         <v>31010975</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C18" s="1">
         <v>31010975</v>
@@ -1092,13 +1204,16 @@
       <c r="D18" s="1">
         <v>30</v>
       </c>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E18" s="5">
+        <v>7.8</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" s="1">
         <v>31010976</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C19" s="1">
         <v>31010976</v>
@@ -1106,13 +1221,16 @@
       <c r="D19" s="1">
         <v>30</v>
       </c>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E19" s="5">
+        <v>6.2</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" s="1">
         <v>31010977</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C20" s="1">
         <v>31010977</v>
@@ -1120,13 +1238,16 @@
       <c r="D20" s="1">
         <v>30</v>
       </c>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E20" s="5">
+        <v>6.15</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" s="1">
         <v>31010979</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C21" s="1">
         <v>31010979</v>
@@ -1134,13 +1255,16 @@
       <c r="D21" s="1">
         <v>200</v>
       </c>
-    </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E21" s="5">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" s="1">
         <v>31010987</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C22" s="1">
         <v>31010987</v>
@@ -1148,13 +1272,16 @@
       <c r="D22" s="1">
         <v>100</v>
       </c>
-    </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E22" s="5">
+        <v>13.5</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" s="1">
         <v>10200052</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C23" s="1">
         <v>10200052</v>
@@ -1162,834 +1289,933 @@
       <c r="D23" s="1">
         <v>500</v>
       </c>
-    </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E23" s="5">
+        <v>3.51</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" s="1">
-        <v>10200053</v>
+        <v>31011665</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C24" s="1">
-        <v>10200053</v>
+        <v>31011665</v>
       </c>
       <c r="D24" s="1">
-        <v>1100</v>
-      </c>
-    </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+      <c r="E24" s="5">
+        <v>15.5</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" s="1">
-        <v>31011665</v>
+        <v>31011666</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C25" s="1">
-        <v>31011665</v>
+        <v>31011666</v>
       </c>
       <c r="D25" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E25" s="5">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" s="1">
-        <v>31011666</v>
+        <v>20000608</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C26" s="1">
-        <v>31011666</v>
-      </c>
-      <c r="D26" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
+        <v>20001578</v>
+      </c>
+      <c r="D26" s="1"/>
+      <c r="E26" s="5">
+        <v>0.36499999999999999</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" s="1">
-        <v>20000608</v>
+        <v>20000609</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C27" s="1">
-        <v>20001578</v>
+        <v>20001580</v>
       </c>
       <c r="D27" s="1"/>
-    </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E27" s="5">
+        <v>0.36899999999999999</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" s="1">
-        <v>20000609</v>
+        <v>20000611</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C28" s="1">
-        <v>20001580</v>
-      </c>
-      <c r="D28" s="1"/>
-    </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
+        <v>20000611</v>
+      </c>
+      <c r="D28" s="1">
+        <v>100</v>
+      </c>
+      <c r="E28" s="5">
+        <v>0.41</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" s="1">
-        <v>20000611</v>
+        <v>20000612</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C29" s="1">
-        <v>20000611</v>
+        <v>20000612</v>
       </c>
       <c r="D29" s="1">
         <v>100</v>
       </c>
-    </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E29" s="5">
+        <v>0.44</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" s="1">
+        <v>20000613</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="C30" s="1">
+        <v>20000613</v>
+      </c>
+      <c r="D30" s="1">
+        <v>1000</v>
+      </c>
+      <c r="E30" s="5">
+        <v>0.45499999999999996</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A31" s="1">
+        <v>20000617</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="C31" s="1">
+        <v>20000617</v>
+      </c>
+      <c r="D31" s="1">
+        <v>1</v>
+      </c>
+      <c r="E31" s="5">
+        <v>191.21949999999998</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A32" s="1">
+        <v>20000677</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C32" s="1">
+        <v>20001580</v>
+      </c>
+      <c r="D32" s="1"/>
+      <c r="E32" s="5">
+        <v>0.43149999999999999</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A33" s="1">
+        <v>10200075</v>
+      </c>
+      <c r="B33" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C33" s="1">
+        <v>10200075</v>
+      </c>
+      <c r="D33" s="1">
+        <v>1500</v>
+      </c>
+      <c r="E33" s="5">
+        <v>0.15945945945945944</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A34" s="1">
+        <v>10200082</v>
+      </c>
+      <c r="B34" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="C34" s="1">
+        <v>10200082</v>
+      </c>
+      <c r="D34" s="1">
+        <v>500</v>
+      </c>
+      <c r="E34" s="5">
+        <v>5.22</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A35" s="1">
+        <v>20000559</v>
+      </c>
+      <c r="B35" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="C35" s="1">
+        <v>20000560</v>
+      </c>
+      <c r="D35" s="1">
+        <v>640</v>
+      </c>
+      <c r="E35" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A36" s="1">
+        <v>10200076</v>
+      </c>
+      <c r="B36" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="C36" s="1">
+        <v>10200008</v>
+      </c>
+      <c r="D36" s="1">
+        <v>1200</v>
+      </c>
+      <c r="E36" s="5">
+        <v>3.1</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A37" s="1">
+        <v>31011007</v>
+      </c>
+      <c r="B37" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="C37" s="1">
+        <v>31011007</v>
+      </c>
+      <c r="D37" s="1"/>
+      <c r="E37" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A38" s="1">
+        <v>20000616</v>
+      </c>
+      <c r="B38" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="C38" s="1">
         <v>20000612</v>
       </c>
-      <c r="B30" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="C30" s="1">
-        <v>20000612</v>
-      </c>
-      <c r="D30" s="1">
+      <c r="D38" s="1">
         <v>100</v>
       </c>
-    </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A31" s="1">
-        <v>20000613</v>
-      </c>
-      <c r="B31" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="C31" s="1">
-        <v>20000613</v>
-      </c>
-      <c r="D31" s="1">
-        <v>1000</v>
-      </c>
-    </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A32" s="1">
-        <v>20000617</v>
-      </c>
-      <c r="B32" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="C32" s="1">
-        <v>20000617</v>
-      </c>
-      <c r="D32" s="1">
+      <c r="E38" s="5">
+        <v>0.442</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A39" s="1">
+        <v>31008291</v>
+      </c>
+      <c r="B39" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="C39" s="1">
+        <v>31008291</v>
+      </c>
+      <c r="D39" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A33" s="1">
-        <v>20000677</v>
-      </c>
-      <c r="B33" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="C33" s="1">
-        <v>20001580</v>
-      </c>
-      <c r="D33" s="1"/>
-    </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A34" s="1">
-        <v>10200075</v>
-      </c>
-      <c r="B34" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="C34" s="1">
-        <v>10200075</v>
-      </c>
-      <c r="D34" s="1">
-        <v>1500</v>
-      </c>
-    </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A35" s="1">
-        <v>10200082</v>
-      </c>
-      <c r="B35" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="C35" s="1">
-        <v>10200082</v>
-      </c>
-      <c r="D35" s="1">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A36" s="1">
-        <v>20000559</v>
-      </c>
-      <c r="B36" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="C36" s="1">
-        <v>20000560</v>
-      </c>
-      <c r="D36" s="1">
-        <v>640</v>
-      </c>
-    </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A37" s="1">
-        <v>10200076</v>
-      </c>
-      <c r="B37" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="C37" s="1">
-        <v>10200008</v>
-      </c>
-      <c r="D37" s="1">
-        <v>1200</v>
-      </c>
-    </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A38" s="1">
-        <v>31011007</v>
-      </c>
-      <c r="B38" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="C38" s="1">
-        <v>31011007</v>
-      </c>
-      <c r="D38" s="1"/>
-    </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A39" s="1">
-        <v>20000616</v>
-      </c>
-      <c r="B39" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="C39" s="1">
-        <v>20000612</v>
-      </c>
-      <c r="D39" s="1">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E39" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A40" s="1">
-        <v>31008291</v>
+        <v>31013438</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="C40" s="1">
-        <v>31008291</v>
+        <v>31013438</v>
       </c>
       <c r="D40" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E40" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A41" s="1">
-        <v>31013438</v>
+        <v>31010639</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="C41" s="1">
-        <v>31013438</v>
-      </c>
-      <c r="D41" s="1">
+        <v>31010639</v>
+      </c>
+      <c r="D41" s="1"/>
+      <c r="E41" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A42" s="1">
+        <v>10200081</v>
+      </c>
+      <c r="B42" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="C42" s="1">
+        <v>10200081</v>
+      </c>
+      <c r="D42" s="1"/>
+      <c r="E42" s="5">
+        <v>0.86</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A43" s="1">
+        <v>10200093</v>
+      </c>
+      <c r="B43" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="C43" s="1">
+        <v>10200011</v>
+      </c>
+      <c r="D43" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A42" s="1">
-        <v>31010639</v>
-      </c>
-      <c r="B42" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="C42" s="1">
-        <v>31010639</v>
-      </c>
-      <c r="D42" s="1"/>
-    </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A43" s="1">
-        <v>10200081</v>
-      </c>
-      <c r="B43" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="C43" s="1">
-        <v>10200081</v>
-      </c>
-      <c r="D43" s="1"/>
-    </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E43" s="5">
+        <v>4.17</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A44" s="1">
-        <v>10200093</v>
+        <v>10200097</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="C44" s="1">
-        <v>10200011</v>
+        <v>10200097</v>
       </c>
       <c r="D44" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E44" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A45" s="1">
-        <v>10200097</v>
+        <v>31010954</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="C45" s="1">
-        <v>10200097</v>
+        <v>10200045</v>
       </c>
       <c r="D45" s="1">
+        <v>1000</v>
+      </c>
+      <c r="E45" s="5">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A46" s="1">
+        <v>10200098</v>
+      </c>
+      <c r="B46" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="C46" s="1">
+        <v>10200098</v>
+      </c>
+      <c r="D46" s="1"/>
+      <c r="E46" s="5">
+        <v>2.2972972972972974</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A47" s="1">
+        <v>10200099</v>
+      </c>
+      <c r="B47" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="C47" s="1">
+        <v>10200099</v>
+      </c>
+      <c r="D47" s="1"/>
+      <c r="E47" s="5">
+        <v>2.4324324324324325</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A48" s="1">
+        <v>10200094</v>
+      </c>
+      <c r="B48" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="C48" s="1">
+        <v>10200094</v>
+      </c>
+      <c r="D48" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A46" s="1">
-        <v>31010954</v>
-      </c>
-      <c r="B46" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="C46" s="1">
-        <v>10200045</v>
-      </c>
-      <c r="D46" s="1">
-        <v>1000</v>
-      </c>
-    </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A47" s="1">
-        <v>10200098</v>
-      </c>
-      <c r="B47" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="C47" s="1">
-        <v>10200098</v>
-      </c>
-      <c r="D47" s="1"/>
-    </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A48" s="1">
-        <v>10200099</v>
-      </c>
-      <c r="B48" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="C48" s="1">
-        <v>10200099</v>
-      </c>
-      <c r="D48" s="1"/>
-    </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E48" s="5">
+        <v>44.5</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A49" s="1">
-        <v>10200094</v>
+        <v>10200085</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="C49" s="1">
-        <v>10200094</v>
+        <v>10200085</v>
       </c>
       <c r="D49" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E49" s="5">
+        <v>127.59</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A50" s="1">
-        <v>10200085</v>
+        <v>10200005</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="C50" s="1">
-        <v>10200085</v>
+        <v>10200005</v>
       </c>
       <c r="D50" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E50" s="5">
+        <v>33.86</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A51" s="1">
-        <v>10200005</v>
+        <v>31015345</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="C51" s="1">
-        <v>10200005</v>
+        <v>31015345</v>
       </c>
       <c r="D51" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E51" s="5">
+        <v>1.62</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A52" s="1">
-        <v>31015345</v>
+        <v>31027175</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="C52" s="1">
-        <v>31015345</v>
-      </c>
-      <c r="D52" s="1">
+        <v>31027175</v>
+      </c>
+      <c r="D52" s="1"/>
+      <c r="E52" s="5">
+        <v>1.4324324324324322</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A53" s="1">
+        <v>31027434</v>
+      </c>
+      <c r="B53" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C53" s="1">
+        <v>31027434</v>
+      </c>
+      <c r="D53" s="1"/>
+      <c r="E53" s="5">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A54" s="1">
+        <v>10200080</v>
+      </c>
+      <c r="B54" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="C54" s="1">
+        <v>10200080</v>
+      </c>
+      <c r="D54" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A53" s="1">
-        <v>31027175</v>
-      </c>
-      <c r="B53" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="C53" s="1">
-        <v>31027175</v>
-      </c>
-      <c r="D53" s="1"/>
-    </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A54" s="1">
-        <v>31027434</v>
-      </c>
-      <c r="B54" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="C54" s="1">
-        <v>31027434</v>
-      </c>
-      <c r="D54" s="1"/>
-    </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E54" s="5">
+        <v>30.3</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A55" s="1">
-        <v>10200080</v>
+        <v>10200155</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="C55" s="1">
-        <v>10200080</v>
+        <v>10200008</v>
       </c>
       <c r="D55" s="1">
+        <v>1200</v>
+      </c>
+      <c r="E55" s="5">
+        <v>2.2999999999999998</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A56" s="1">
+        <v>10200156</v>
+      </c>
+      <c r="B56" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="C56" s="1">
+        <v>10200011</v>
+      </c>
+      <c r="D56" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A56" s="1">
-        <v>20000610</v>
-      </c>
-      <c r="B56" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="C56" s="1">
-        <v>20000613</v>
-      </c>
-      <c r="D56" s="1">
-        <v>1000</v>
-      </c>
-    </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E56" s="5">
+        <v>10.28</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A57" s="1">
-        <v>10200155</v>
+        <v>32005313</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="C57" s="1">
+        <v>32005313</v>
+      </c>
+      <c r="D57" s="1"/>
+      <c r="E57" s="5">
+        <v>138.64864864864865</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A58" s="1">
+        <v>32004433</v>
+      </c>
+      <c r="B58" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="C58" s="1">
+        <v>32004433</v>
+      </c>
+      <c r="D58" s="1"/>
+      <c r="E58" s="5">
+        <v>0.64864864864864857</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A59" s="1">
+        <v>10200046</v>
+      </c>
+      <c r="B59" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="C59" s="1">
+        <v>10200046</v>
+      </c>
+      <c r="D59" s="1"/>
+      <c r="E59" s="5">
+        <v>0.14054054054054055</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A60" s="1">
+        <v>10200168</v>
+      </c>
+      <c r="B60" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="C60" s="1">
+        <v>10200011</v>
+      </c>
+      <c r="D60" s="1">
+        <v>1</v>
+      </c>
+      <c r="E60" s="5">
+        <v>9.25</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A61" s="1">
+        <v>32007249</v>
+      </c>
+      <c r="B61" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="C61" s="1">
+        <v>32007249</v>
+      </c>
+      <c r="D61" s="1"/>
+      <c r="E61" s="5">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A62" s="1">
+        <v>10200177</v>
+      </c>
+      <c r="B62" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="C62" s="1">
         <v>10200008</v>
       </c>
-      <c r="D57" s="1">
+      <c r="D62" s="1">
         <v>1200</v>
       </c>
-    </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A58" s="1">
-        <v>10200156</v>
-      </c>
-      <c r="B58" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="C58" s="1">
-        <v>10200011</v>
-      </c>
-      <c r="D58" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="59" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A59" s="1">
-        <v>20000576</v>
-      </c>
-      <c r="B59" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="C59" s="1">
-        <v>20000579</v>
-      </c>
-      <c r="D59" s="1">
+      <c r="E62" s="5">
+        <v>2.12</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A63" s="1">
+        <v>31028016</v>
+      </c>
+      <c r="B63" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="C63" s="1">
+        <v>31028016</v>
+      </c>
+      <c r="D63" s="1">
+        <v>1150</v>
+      </c>
+      <c r="E63" s="5">
+        <v>3.2</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A64" s="1">
+        <v>31010981</v>
+      </c>
+      <c r="B64" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="C64" s="1">
+        <v>31010981</v>
+      </c>
+      <c r="D64" s="1">
         <v>50</v>
       </c>
-    </row>
-    <row r="60" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A60" s="1">
-        <v>32005313</v>
-      </c>
-      <c r="B60" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="C60" s="1">
-        <v>32005313</v>
-      </c>
-      <c r="D60" s="1"/>
-    </row>
-    <row r="61" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A61" s="1">
-        <v>32004433</v>
-      </c>
-      <c r="B61" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="C61" s="1">
-        <v>32004433</v>
-      </c>
-      <c r="D61" s="1"/>
-    </row>
-    <row r="62" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A62" s="1">
-        <v>10200046</v>
-      </c>
-      <c r="B62" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="C62" s="1">
-        <v>10200046</v>
-      </c>
-      <c r="D62" s="1"/>
-    </row>
-    <row r="63" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A63" s="1">
-        <v>10200003</v>
-      </c>
-      <c r="B63" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="C63" s="1">
-        <v>10200003</v>
-      </c>
-      <c r="D63" s="1"/>
-    </row>
-    <row r="64" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A64" s="1">
-        <v>10200168</v>
-      </c>
-      <c r="B64" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="C64" s="1">
-        <v>10200011</v>
-      </c>
-      <c r="D64" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="65" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E64" s="5">
+        <v>2.4</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A65" s="1">
-        <v>32007249</v>
+        <v>20001578</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="C65" s="1">
-        <v>32007249</v>
+        <v>20001578</v>
       </c>
       <c r="D65" s="1"/>
-    </row>
-    <row r="66" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E65" s="5">
+        <v>0.371</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A66" s="1">
-        <v>20000556</v>
+        <v>20001579</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="C66" s="1">
-        <v>20000556</v>
+        <v>20001580</v>
       </c>
       <c r="D66" s="1"/>
-    </row>
-    <row r="67" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E66" s="5">
+        <v>0.378</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A67" s="1">
-        <v>20000557</v>
+        <v>20001580</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="C67" s="1">
-        <v>20000557</v>
+        <v>20001580</v>
       </c>
       <c r="D67" s="1"/>
-    </row>
-    <row r="68" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E67" s="5">
+        <v>0.39200000000000002</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A68" s="1">
-        <v>10200177</v>
-      </c>
-      <c r="B68" s="1" t="s">
-        <v>69</v>
+        <v>10200189</v>
+      </c>
+      <c r="B68" s="4" t="s">
+        <v>71</v>
       </c>
       <c r="C68" s="1">
-        <v>10200008</v>
-      </c>
-      <c r="D68" s="1">
-        <v>1200</v>
-      </c>
-    </row>
-    <row r="69" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A69" s="1">
-        <v>31028016</v>
-      </c>
-      <c r="B69" s="1" t="s">
-        <v>70</v>
+        <v>10200189</v>
+      </c>
+      <c r="D68" s="1"/>
+      <c r="E68" s="5">
+        <v>2.98</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A69">
+        <v>10200227</v>
+      </c>
+      <c r="B69" s="4" t="s">
+        <v>72</v>
       </c>
       <c r="C69" s="1">
-        <v>31028016</v>
-      </c>
-      <c r="D69" s="1">
-        <v>1150</v>
-      </c>
-    </row>
-    <row r="70" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A70" s="1">
-        <v>31010981</v>
-      </c>
-      <c r="B70" s="1" t="s">
-        <v>71</v>
+        <v>10200227</v>
+      </c>
+      <c r="D69" s="1"/>
+      <c r="E69" s="5">
+        <v>3.51</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A70">
+        <v>10200228</v>
+      </c>
+      <c r="B70" s="4" t="s">
+        <v>73</v>
       </c>
       <c r="C70" s="1">
-        <v>31010981</v>
-      </c>
-      <c r="D70" s="1">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="71" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A71" s="1">
-        <v>20001578</v>
-      </c>
-      <c r="B71" s="1" t="s">
-        <v>72</v>
+        <v>10200228</v>
+      </c>
+      <c r="D70" s="1"/>
+      <c r="E70" s="5">
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A71">
+        <v>10200265</v>
+      </c>
+      <c r="B71" s="4" t="s">
+        <v>74</v>
       </c>
       <c r="C71" s="1">
-        <v>20001578</v>
+        <v>10200265</v>
       </c>
       <c r="D71" s="1"/>
-    </row>
-    <row r="72" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A72" s="1">
-        <v>20001579</v>
-      </c>
-      <c r="B72" s="1" t="s">
-        <v>73</v>
+      <c r="E71" s="5">
+        <v>4.96</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A72">
+        <v>10200266</v>
+      </c>
+      <c r="B72" s="4" t="s">
+        <v>75</v>
       </c>
       <c r="C72" s="1">
-        <v>20001580</v>
+        <v>10200266</v>
       </c>
       <c r="D72" s="1"/>
-    </row>
-    <row r="73" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A73" s="1">
-        <v>20001580</v>
-      </c>
-      <c r="B73" s="1" t="s">
-        <v>74</v>
+      <c r="E72" s="5">
+        <v>3.91</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A73">
+        <v>10200267</v>
+      </c>
+      <c r="B73" s="4" t="s">
+        <v>76</v>
       </c>
       <c r="C73" s="1">
-        <v>20001580</v>
+        <v>10200267</v>
       </c>
       <c r="D73" s="1"/>
-    </row>
-    <row r="74" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A74" s="4">
-        <v>10200189</v>
-      </c>
-      <c r="B74" s="5" t="s">
-        <v>97</v>
-      </c>
-      <c r="C74" s="4">
-        <v>10200189</v>
-      </c>
-      <c r="D74" s="4"/>
-    </row>
-    <row r="75" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E73" s="5">
+        <v>4.84</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A74">
+        <v>20001668</v>
+      </c>
+      <c r="B74" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="C74" s="1">
+        <v>20001668</v>
+      </c>
+      <c r="D74" s="1"/>
+      <c r="E74" s="5">
+        <v>0.372</v>
+      </c>
+    </row>
+    <row r="75" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A75">
-        <v>10200227</v>
-      </c>
-      <c r="B75" s="5" t="s">
-        <v>98</v>
-      </c>
-      <c r="C75" s="4">
-        <v>10200227</v>
-      </c>
-      <c r="D75" s="4"/>
-    </row>
-    <row r="76" spans="1:4" x14ac:dyDescent="0.25">
+        <v>20001688</v>
+      </c>
+      <c r="B75" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="C75" s="1">
+        <v>20001688</v>
+      </c>
+      <c r="D75" s="1"/>
+      <c r="E75" s="5">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="76" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A76">
-        <v>10200228</v>
-      </c>
-      <c r="B76" s="5" t="s">
-        <v>99</v>
-      </c>
-      <c r="C76" s="4">
-        <v>10200228</v>
-      </c>
-      <c r="D76" s="4"/>
-    </row>
-    <row r="77" spans="1:4" x14ac:dyDescent="0.25">
+        <v>30000517</v>
+      </c>
+      <c r="B76" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="C76" s="1">
+        <v>30000517</v>
+      </c>
+      <c r="D76" s="1"/>
+      <c r="E76" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A77">
-        <v>10200265</v>
-      </c>
-      <c r="B77" s="5" t="s">
-        <v>100</v>
-      </c>
-      <c r="C77" s="4">
-        <v>10200265</v>
-      </c>
-      <c r="D77" s="4"/>
-    </row>
-    <row r="78" spans="1:4" x14ac:dyDescent="0.25">
+        <v>30000527</v>
+      </c>
+      <c r="B77" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="C77" s="1">
+        <v>30000527</v>
+      </c>
+      <c r="D77" s="1"/>
+      <c r="E77" s="5">
+        <v>3.5729729729729729</v>
+      </c>
+    </row>
+    <row r="78" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A78">
-        <v>10200266</v>
-      </c>
-      <c r="B78" s="5" t="s">
-        <v>101</v>
-      </c>
-      <c r="C78" s="4">
-        <v>10200266</v>
-      </c>
-      <c r="D78" s="4"/>
-    </row>
-    <row r="79" spans="1:4" x14ac:dyDescent="0.25">
+        <v>30000528</v>
+      </c>
+      <c r="B78" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="C78" s="1">
+        <v>30000528</v>
+      </c>
+      <c r="D78" s="1"/>
+      <c r="E78" s="5">
+        <v>3.0426486486486484</v>
+      </c>
+    </row>
+    <row r="79" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A79">
-        <v>10200267</v>
-      </c>
-      <c r="B79" s="5" t="s">
-        <v>102</v>
-      </c>
-      <c r="C79" s="4">
-        <v>10200267</v>
-      </c>
-      <c r="D79" s="4"/>
-    </row>
-    <row r="80" spans="1:4" x14ac:dyDescent="0.25">
+        <v>31013555</v>
+      </c>
+      <c r="B79" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="C79" s="1">
+        <v>31013555</v>
+      </c>
+      <c r="D79" s="1"/>
+      <c r="E79" s="5">
+        <v>1.95</v>
+      </c>
+    </row>
+    <row r="80" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A80">
-        <v>20001668</v>
-      </c>
-      <c r="B80" s="5" t="s">
-        <v>103</v>
-      </c>
-      <c r="C80" s="4">
-        <v>20001668</v>
-      </c>
-      <c r="D80" s="4"/>
-    </row>
-    <row r="81" spans="1:4" x14ac:dyDescent="0.25">
+        <v>31029889</v>
+      </c>
+      <c r="B80" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="C80" s="1">
+        <v>31029889</v>
+      </c>
+      <c r="D80" s="1"/>
+      <c r="E80" s="5">
+        <v>3.65</v>
+      </c>
+    </row>
+    <row r="81" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A81">
-        <v>20001688</v>
-      </c>
-      <c r="B81" s="5" t="s">
-        <v>104</v>
-      </c>
-      <c r="C81" s="4">
-        <v>20001688</v>
-      </c>
-      <c r="D81" s="4"/>
-    </row>
-    <row r="82" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A82">
-        <v>30000517</v>
-      </c>
-      <c r="B82" s="5" t="s">
-        <v>105</v>
-      </c>
-      <c r="C82" s="4">
-        <v>30000517</v>
-      </c>
-      <c r="D82" s="4"/>
-    </row>
-    <row r="83" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A83">
-        <v>30000527</v>
-      </c>
-      <c r="B83" s="5" t="s">
-        <v>106</v>
-      </c>
-      <c r="C83" s="4">
-        <v>30000527</v>
-      </c>
-      <c r="D83" s="4"/>
-    </row>
-    <row r="84" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A84">
-        <v>30000528</v>
-      </c>
-      <c r="B84" s="5" t="s">
-        <v>107</v>
-      </c>
-      <c r="C84" s="4">
-        <v>30000528</v>
-      </c>
-      <c r="D84" s="4"/>
-    </row>
-    <row r="85" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A85">
-        <v>31013555</v>
-      </c>
-      <c r="B85" s="5" t="s">
-        <v>108</v>
-      </c>
-      <c r="C85" s="4">
-        <v>31013555</v>
-      </c>
-      <c r="D85" s="4"/>
-    </row>
-    <row r="86" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A86">
-        <v>31029889</v>
-      </c>
-      <c r="B86" s="5" t="s">
-        <v>109</v>
-      </c>
-      <c r="C86" s="4">
-        <v>31029889</v>
-      </c>
-      <c r="D86" s="4"/>
-    </row>
-    <row r="87" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A87">
         <v>31029890</v>
       </c>
-      <c r="B87" s="5" t="s">
-        <v>110</v>
-      </c>
-      <c r="C87" s="4">
+      <c r="B81" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="C81" s="1">
         <v>31029890</v>
       </c>
-      <c r="D87" s="4"/>
+      <c r="D81" s="1"/>
+      <c r="E81" s="5">
+        <v>6.15</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2002,4476 +2228,5695 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E460D34A-B63B-4552-8467-8A3C0E85FA66}">
   <sheetPr codeName="Hoja2"/>
-  <dimension ref="A1:C406"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:D406"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="3" max="3" width="15.7109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="21.85546875" style="6" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+        <v>86</v>
+      </c>
+      <c r="D1" s="5" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
         <v>10200012</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="C2" s="1">
         <v>0.7</v>
       </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D2" s="5" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" s="1">
         <v>10200093</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="C3" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D3" s="5" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
         <v>10200008</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="C4" s="1">
         <v>0.5</v>
       </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D4" s="5" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
         <v>10200005</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="C5" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D5" s="5" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
         <v>20000560</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="C6" s="1">
         <v>0.52</v>
       </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D6" s="5" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
         <v>20000579</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="C7" s="1">
         <v>2.073525813555175E-2</v>
       </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D7" s="5" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
         <v>31011665</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="C8" s="1">
         <v>1.5E-3</v>
       </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D8" s="5" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" s="1">
         <v>31011666</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="C9" s="1">
         <v>2.3397285914833881E-4</v>
       </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D9" s="5" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" s="1">
         <v>10200080</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="C10" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D10" s="5" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" s="1">
         <v>10200085</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="C11" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D11" s="5" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" s="1">
         <v>20001578</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="C12" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D12" s="5" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" s="1">
         <v>20000612</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="C13" s="1">
         <v>1.4999999999999999E-2</v>
       </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D13" s="5" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" s="1">
         <v>20001668</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="C14" s="1">
         <v>0.51760645765091251</v>
       </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D14" s="5" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" s="1">
         <v>20001580</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="C15" s="1">
         <v>20.2</v>
       </c>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D15" s="5" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" s="1">
         <v>20001688</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="C16" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D16" s="5" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" s="1">
         <v>20000617</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="C17" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D17" s="5" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" s="1">
         <v>10200189</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="C18" s="1">
         <v>0.15</v>
       </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D18" s="5" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" s="1">
         <v>31013555</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="C19" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D19" s="5" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20" s="1">
         <v>10200009</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="C20" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D20" s="5" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A21" s="1">
         <v>10200227</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="C21" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D21" s="5" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A22" s="1">
         <v>10200045</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="C22" s="1">
         <v>1.54</v>
       </c>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D22" s="5" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A23" s="1">
         <v>32004433</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="C23" s="1">
         <v>5.8661921569010877E-3</v>
       </c>
-    </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D23" s="5" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A24" s="1">
         <v>32004434</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="C24" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D24" s="5" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A25" s="1">
         <v>31010981</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="C25" s="1">
         <v>0.21</v>
       </c>
-    </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D25" s="5" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A26" s="1">
         <v>31010971</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="C26" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D26" s="5" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A27" s="1">
         <v>31029889</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="C27" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D27" s="5" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A28" s="1">
         <v>31010973</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="C28" s="1">
         <v>0.02</v>
       </c>
-    </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D28" s="5" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A29" s="1">
         <v>31010975</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="C29" s="1">
         <v>5.0000000000000001E-3</v>
       </c>
-    </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D29" s="5" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A30" s="1">
         <v>31010976</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="C30" s="1">
         <v>1.2595424077992138E-2</v>
       </c>
-    </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D30" s="5" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A31" s="1">
         <v>31010977</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="C31" s="1">
         <v>0.01</v>
       </c>
-    </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D31" s="5" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A32" s="1">
         <v>31029890</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="C32" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D32" s="5" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A33" s="1">
         <v>10200075</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="C33" s="1">
         <v>0.42</v>
       </c>
-    </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D33" s="5" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A34" s="1">
         <v>10200021</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="C34" s="1">
         <v>22</v>
       </c>
-    </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D34" s="5" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A35" s="1">
         <v>10200228</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="C35" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D35" s="5" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A36" s="1">
         <v>10200023</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="C36" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D36" s="5" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A37" s="1">
         <v>10200266</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="C37" s="1">
         <v>0.2</v>
       </c>
-    </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D37" s="5" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A38" s="1">
         <v>10200267</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="C38" s="1">
         <v>0.3</v>
       </c>
-    </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D38" s="5" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A39" s="1">
         <v>10200265</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="C39" s="1">
         <v>0.85</v>
       </c>
-    </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D39" s="5" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A40" s="1">
         <v>10200082</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="C40" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D40" s="5" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A41" s="1">
         <v>31015345</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="C41" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D41" s="5" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A42" s="1">
         <v>31010979</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="C42" s="1">
         <v>5.2999999999999999E-2</v>
       </c>
-    </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D42" s="5" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A43" s="1">
         <v>31010987</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="C43" s="1">
         <v>0.01</v>
       </c>
-    </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D43" s="5" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A44" s="1">
         <v>30000527</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="C44" s="1">
         <v>5.526906878802059</v>
       </c>
-    </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D44" s="5" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A45" s="1">
         <v>30000528</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="C45" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D45" s="5" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A46" s="1">
         <v>30000517</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="C46" s="1">
         <v>42</v>
       </c>
-    </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D46" s="5" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A47" s="1">
         <v>10200012</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>79</v>
+        <v>100</v>
       </c>
       <c r="C47" s="1">
         <v>0.7</v>
       </c>
-    </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D47" s="5" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A48" s="1">
         <v>10200093</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>79</v>
+        <v>100</v>
       </c>
       <c r="C48" s="1">
         <v>4.0999999999999996</v>
       </c>
-    </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D48" s="5" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A49" s="1">
         <v>10200008</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>79</v>
+        <v>100</v>
       </c>
       <c r="C49" s="1">
         <v>0.3</v>
       </c>
-    </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D49" s="5" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A50" s="1">
         <v>10200005</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>79</v>
+        <v>100</v>
       </c>
       <c r="C50" s="1">
         <v>5.622399640166422E-4</v>
       </c>
-    </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D50" s="5" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A51" s="1">
         <v>20000560</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>79</v>
+        <v>100</v>
       </c>
       <c r="C51" s="1">
         <v>0.52</v>
       </c>
-    </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D51" s="5" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A52" s="1">
         <v>20000579</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>79</v>
+        <v>100</v>
       </c>
       <c r="C52" s="1">
         <v>2.073525813555175E-2</v>
       </c>
-    </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D52" s="5" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A53" s="1">
         <v>31011665</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>79</v>
+        <v>100</v>
       </c>
       <c r="C53" s="1">
         <v>4.8884934640842405E-4</v>
       </c>
-    </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D53" s="5" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="54" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A54" s="1">
         <v>31011666</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>79</v>
+        <v>100</v>
       </c>
       <c r="C54" s="1">
         <v>1.1100473157668345E-4</v>
       </c>
-    </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D54" s="5" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="55" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A55" s="1">
         <v>10200080</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>79</v>
+        <v>100</v>
       </c>
       <c r="C55" s="1">
         <v>1.9553973856336961E-4</v>
       </c>
-    </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D55" s="5" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="56" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A56" s="1">
         <v>10200085</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>79</v>
+        <v>100</v>
       </c>
       <c r="C56" s="1">
         <v>1.7889354343386156E-4</v>
       </c>
-    </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D56" s="5" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="57" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A57" s="1">
         <v>20001578</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>79</v>
+        <v>100</v>
       </c>
       <c r="C57" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D57" s="5" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="58" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A58" s="1">
         <v>20000612</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>79</v>
+        <v>100</v>
       </c>
       <c r="C58" s="1">
         <v>1.4999999999999999E-2</v>
       </c>
-    </row>
-    <row r="59" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D58" s="5" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="59" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A59" s="1">
         <v>20001668</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>79</v>
+        <v>100</v>
       </c>
       <c r="C59" s="1">
         <v>0.51760645765091251</v>
       </c>
-    </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D59" s="5" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="60" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A60" s="1">
         <v>20001580</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>79</v>
+        <v>100</v>
       </c>
       <c r="C60" s="1">
         <v>20.2</v>
       </c>
-    </row>
-    <row r="61" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D60" s="5" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="61" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A61" s="1">
         <v>20001688</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>79</v>
+        <v>100</v>
       </c>
       <c r="C61" s="1">
         <v>0.01</v>
       </c>
-    </row>
-    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D61" s="5" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="62" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A62" s="1">
         <v>20000617</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>79</v>
+        <v>100</v>
       </c>
       <c r="C62" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D62" s="5" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="63" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A63" s="1">
         <v>10200189</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>79</v>
+        <v>100</v>
       </c>
       <c r="C63" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D63" s="5" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="64" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A64" s="1">
         <v>31013555</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>79</v>
+        <v>100</v>
       </c>
       <c r="C64" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D64" s="5" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="65" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A65" s="1">
         <v>10200009</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>79</v>
+        <v>100</v>
       </c>
       <c r="C65" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D65" s="5" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="66" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A66" s="1">
         <v>10200227</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>79</v>
+        <v>100</v>
       </c>
       <c r="C66" s="1">
         <v>0.3</v>
       </c>
-    </row>
-    <row r="67" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D66" s="5" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="67" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A67" s="1">
         <v>10200045</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>79</v>
+        <v>100</v>
       </c>
       <c r="C67" s="1">
         <v>1.8</v>
       </c>
-    </row>
-    <row r="68" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D67" s="5" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="68" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A68" s="1">
         <v>32004433</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>79</v>
+        <v>100</v>
       </c>
       <c r="C68" s="1">
         <v>5.8661921569010877E-3</v>
       </c>
-    </row>
-    <row r="69" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D68" s="5" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="69" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A69" s="1">
         <v>32004434</v>
       </c>
       <c r="B69" s="1" t="s">
-        <v>79</v>
+        <v>100</v>
       </c>
       <c r="C69" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D69" s="5" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="70" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A70" s="1">
         <v>31010981</v>
       </c>
       <c r="B70" s="1" t="s">
-        <v>79</v>
+        <v>100</v>
       </c>
       <c r="C70" s="1">
         <v>0.2</v>
       </c>
-    </row>
-    <row r="71" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D70" s="5" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="71" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A71" s="1">
         <v>31010971</v>
       </c>
       <c r="B71" s="1" t="s">
-        <v>79</v>
+        <v>100</v>
       </c>
       <c r="C71" s="1">
         <v>1.6650709736502518E-3</v>
       </c>
-    </row>
-    <row r="72" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D71" s="5" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="72" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A72" s="1">
         <v>31029889</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>79</v>
+        <v>100</v>
       </c>
       <c r="C72" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="73" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D72" s="5" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="73" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A73" s="1">
         <v>31010973</v>
       </c>
       <c r="B73" s="1" t="s">
-        <v>79</v>
+        <v>100</v>
       </c>
       <c r="C73" s="1">
         <v>3.5000000000000003E-2</v>
       </c>
-    </row>
-    <row r="74" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D73" s="5" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="74" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A74" s="1">
         <v>31010975</v>
       </c>
       <c r="B74" s="1" t="s">
-        <v>79</v>
+        <v>100</v>
       </c>
       <c r="C74" s="1">
         <v>3.5778708686772312E-3</v>
       </c>
-    </row>
-    <row r="75" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D74" s="5" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="75" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A75" s="1">
         <v>31010976</v>
       </c>
       <c r="B75" s="1" t="s">
-        <v>79</v>
+        <v>100</v>
       </c>
       <c r="C75" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D75" s="5" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="76" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A76" s="1">
         <v>31010977</v>
       </c>
       <c r="B76" s="1" t="s">
-        <v>79</v>
+        <v>100</v>
       </c>
       <c r="C76" s="1">
         <v>0.02</v>
       </c>
-    </row>
-    <row r="77" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D76" s="5" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="77" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A77" s="1">
         <v>31029890</v>
       </c>
       <c r="B77" s="1" t="s">
-        <v>79</v>
+        <v>100</v>
       </c>
       <c r="C77" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="78" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D77" s="5" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="78" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A78" s="1">
         <v>10200075</v>
       </c>
       <c r="B78" s="1" t="s">
-        <v>79</v>
+        <v>100</v>
       </c>
       <c r="C78" s="1">
         <v>0.5</v>
       </c>
-    </row>
-    <row r="79" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D78" s="5" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="79" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A79" s="1">
         <v>10200021</v>
       </c>
       <c r="B79" s="1" t="s">
-        <v>79</v>
+        <v>100</v>
       </c>
       <c r="C79" s="1">
         <v>19.524453256607881</v>
       </c>
-    </row>
-    <row r="80" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D79" s="5" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="80" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A80" s="1">
         <v>10200228</v>
       </c>
       <c r="B80" s="1" t="s">
-        <v>79</v>
+        <v>100</v>
       </c>
       <c r="C80" s="1">
         <v>5</v>
       </c>
-    </row>
-    <row r="81" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D80" s="5" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="81" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A81" s="1">
         <v>10200023</v>
       </c>
       <c r="B81" s="1" t="s">
-        <v>79</v>
+        <v>100</v>
       </c>
       <c r="C81" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="82" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D81" s="5" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="82" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A82" s="1">
         <v>10200266</v>
       </c>
       <c r="B82" s="1" t="s">
-        <v>79</v>
+        <v>100</v>
       </c>
       <c r="C82" s="1">
         <v>0.11</v>
       </c>
-    </row>
-    <row r="83" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D82" s="5" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="83" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A83" s="1">
         <v>10200267</v>
       </c>
       <c r="B83" s="1" t="s">
-        <v>79</v>
+        <v>100</v>
       </c>
       <c r="C83" s="1">
         <v>0.11</v>
       </c>
-    </row>
-    <row r="84" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D83" s="5" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="84" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A84" s="1">
         <v>10200265</v>
       </c>
       <c r="B84" s="1" t="s">
-        <v>79</v>
+        <v>100</v>
       </c>
       <c r="C84" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D84" s="5" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="85" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A85" s="1">
         <v>10200082</v>
       </c>
       <c r="B85" s="1" t="s">
-        <v>79</v>
+        <v>100</v>
       </c>
       <c r="C85" s="1">
         <v>0.88000000000000012</v>
       </c>
-    </row>
-    <row r="86" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D85" s="5" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="86" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A86" s="1">
         <v>31015345</v>
       </c>
       <c r="B86" s="1" t="s">
-        <v>79</v>
+        <v>100</v>
       </c>
       <c r="C86" s="1">
         <v>0.5</v>
       </c>
-    </row>
-    <row r="87" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D86" s="5" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="87" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A87" s="1">
         <v>31010979</v>
       </c>
       <c r="B87" s="1" t="s">
-        <v>79</v>
+        <v>100</v>
       </c>
       <c r="C87" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D87" s="5" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="88" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A88" s="1">
         <v>31010987</v>
       </c>
       <c r="B88" s="1" t="s">
-        <v>79</v>
+        <v>100</v>
       </c>
       <c r="C88" s="1">
         <v>1.4999999999999999E-2</v>
       </c>
-    </row>
-    <row r="89" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D88" s="5" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="89" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A89" s="1">
         <v>30000527</v>
       </c>
       <c r="B89" s="1" t="s">
-        <v>79</v>
+        <v>100</v>
       </c>
       <c r="C89" s="1">
         <v>0.96685997107887711</v>
       </c>
-    </row>
-    <row r="90" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D89" s="5" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="90" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A90" s="1">
         <v>30000528</v>
       </c>
       <c r="B90" s="1" t="s">
-        <v>79</v>
+        <v>100</v>
       </c>
       <c r="C90" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="91" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D90" s="5" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="91" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A91" s="1">
         <v>30000517</v>
       </c>
       <c r="B91" s="1" t="s">
-        <v>79</v>
+        <v>100</v>
       </c>
       <c r="C91" s="1">
         <v>41</v>
       </c>
-    </row>
-    <row r="92" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D91" s="5" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="92" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A92" s="1">
         <v>10200012</v>
       </c>
       <c r="B92" s="1" t="s">
-        <v>80</v>
+        <v>101</v>
       </c>
       <c r="C92" s="1">
         <v>0.7</v>
       </c>
-    </row>
-    <row r="93" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D92" s="5" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="93" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A93" s="1">
         <v>10200093</v>
       </c>
       <c r="B93" s="1" t="s">
-        <v>80</v>
+        <v>101</v>
       </c>
       <c r="C93" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D93" s="5" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="94" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A94" s="1">
         <v>10200008</v>
       </c>
       <c r="B94" s="1" t="s">
-        <v>80</v>
+        <v>101</v>
       </c>
       <c r="C94" s="1">
         <v>0.3</v>
       </c>
-    </row>
-    <row r="95" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D94" s="5" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="95" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A95" s="1">
         <v>10200005</v>
       </c>
       <c r="B95" s="1" t="s">
-        <v>80</v>
+        <v>101</v>
       </c>
       <c r="C95" s="1">
         <v>1.5877426269201762E-3</v>
       </c>
-    </row>
-    <row r="96" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D95" s="5" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="96" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A96" s="1">
         <v>20000560</v>
       </c>
       <c r="B96" s="1" t="s">
-        <v>80</v>
+        <v>101</v>
       </c>
       <c r="C96" s="1">
         <v>0.52</v>
       </c>
-    </row>
-    <row r="97" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D96" s="5" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="97" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A97" s="1">
         <v>20000579</v>
       </c>
       <c r="B97" s="1" t="s">
-        <v>80</v>
+        <v>101</v>
       </c>
       <c r="C97" s="1">
         <v>2.073525813555175E-2</v>
       </c>
-    </row>
-    <row r="98" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D97" s="5" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="98" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A98" s="1">
         <v>31011665</v>
       </c>
       <c r="B98" s="1" t="s">
-        <v>80</v>
+        <v>101</v>
       </c>
       <c r="C98" s="1">
         <v>1.3413816230717639E-3</v>
       </c>
-    </row>
-    <row r="99" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D98" s="5" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="99" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A99" s="1">
         <v>31011666</v>
       </c>
       <c r="B99" s="1" t="s">
-        <v>80</v>
+        <v>101</v>
       </c>
       <c r="C99" s="1">
         <v>2.8949673685357266E-4</v>
       </c>
-    </row>
-    <row r="100" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D99" s="5" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="100" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A100" s="1">
         <v>10200080</v>
       </c>
       <c r="B100" s="1" t="s">
-        <v>80</v>
+        <v>101</v>
       </c>
       <c r="C100" s="1">
         <v>7.9828369006635736E-4</v>
       </c>
-    </row>
-    <row r="101" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D100" s="5" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="101" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A101" s="1">
         <v>10200085</v>
       </c>
       <c r="B101" s="1" t="s">
-        <v>80</v>
+        <v>101</v>
       </c>
       <c r="C101" s="1">
         <v>5.9871276754976804E-4</v>
       </c>
-    </row>
-    <row r="102" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D101" s="5" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="102" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A102" s="1">
         <v>20001578</v>
       </c>
       <c r="B102" s="1" t="s">
-        <v>80</v>
+        <v>101</v>
       </c>
       <c r="C102" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="103" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D102" s="5" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="103" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A103" s="1">
         <v>20000612</v>
       </c>
       <c r="B103" s="1" t="s">
-        <v>80</v>
+        <v>101</v>
       </c>
       <c r="C103" s="1">
         <v>0.02</v>
       </c>
-    </row>
-    <row r="104" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D103" s="5" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="104" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A104" s="1">
         <v>20001668</v>
       </c>
       <c r="B104" s="1" t="s">
-        <v>80</v>
+        <v>101</v>
       </c>
       <c r="C104" s="1">
         <v>0.7</v>
       </c>
-    </row>
-    <row r="105" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D104" s="5" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="105" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A105" s="1">
         <v>20001580</v>
       </c>
       <c r="B105" s="1" t="s">
-        <v>80</v>
+        <v>101</v>
       </c>
       <c r="C105" s="1">
         <v>20.2</v>
       </c>
-    </row>
-    <row r="106" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D105" s="5" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="106" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A106" s="1">
         <v>20001688</v>
       </c>
       <c r="B106" s="1" t="s">
-        <v>80</v>
+        <v>101</v>
       </c>
       <c r="C106" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="107" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D106" s="5" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="107" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A107" s="1">
         <v>20000617</v>
       </c>
       <c r="B107" s="1" t="s">
-        <v>80</v>
+        <v>101</v>
       </c>
       <c r="C107" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="108" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D107" s="5" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="108" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A108" s="1">
         <v>10200189</v>
       </c>
       <c r="B108" s="1" t="s">
-        <v>80</v>
+        <v>101</v>
       </c>
       <c r="C108" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="109" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D108" s="5" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="109" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A109" s="1">
         <v>31013555</v>
       </c>
       <c r="B109" s="1" t="s">
-        <v>80</v>
+        <v>101</v>
       </c>
       <c r="C109" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="110" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D109" s="5" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="110" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A110" s="1">
         <v>10200009</v>
       </c>
       <c r="B110" s="1" t="s">
-        <v>80</v>
+        <v>101</v>
       </c>
       <c r="C110" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="111" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D110" s="5" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="111" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A111" s="1">
         <v>10200227</v>
       </c>
       <c r="B111" s="1" t="s">
-        <v>80</v>
+        <v>101</v>
       </c>
       <c r="C111" s="1">
         <v>0.3</v>
       </c>
-    </row>
-    <row r="112" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D111" s="5" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="112" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A112" s="1">
         <v>10200045</v>
       </c>
       <c r="B112" s="1" t="s">
-        <v>80</v>
+        <v>101</v>
       </c>
       <c r="C112" s="1">
         <v>2</v>
       </c>
-    </row>
-    <row r="113" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D112" s="5" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="113" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A113" s="1">
         <v>32004433</v>
       </c>
       <c r="B113" s="1" t="s">
-        <v>80</v>
+        <v>101</v>
       </c>
       <c r="C113" s="1">
         <v>8.854912262577664E-3</v>
       </c>
-    </row>
-    <row r="114" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D113" s="5" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="114" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A114" s="1">
         <v>32004434</v>
       </c>
       <c r="B114" s="1" t="s">
-        <v>80</v>
+        <v>101</v>
       </c>
       <c r="C114" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="115" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D114" s="5" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="115" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A115" s="1">
         <v>31010981</v>
       </c>
       <c r="B115" s="1" t="s">
-        <v>80</v>
+        <v>101</v>
       </c>
       <c r="C115" s="1">
         <v>0.5</v>
       </c>
-    </row>
-    <row r="116" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D115" s="5" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="116" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A116" s="1">
         <v>31010971</v>
       </c>
       <c r="B116" s="1" t="s">
-        <v>80</v>
+        <v>101</v>
       </c>
       <c r="C116" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="117" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D116" s="5" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="117" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A117" s="1">
         <v>31029889</v>
       </c>
       <c r="B117" s="1" t="s">
-        <v>80</v>
+        <v>101</v>
       </c>
       <c r="C117" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="118" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D117" s="5" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="118" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A118" s="1">
         <v>31010973</v>
       </c>
       <c r="B118" s="1" t="s">
-        <v>80</v>
+        <v>101</v>
       </c>
       <c r="C118" s="1">
         <v>2.5000000000000001E-2</v>
       </c>
-    </row>
-    <row r="119" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D118" s="5" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="119" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A119" s="1">
         <v>31010975</v>
       </c>
       <c r="B119" s="1" t="s">
-        <v>80</v>
+        <v>101</v>
       </c>
       <c r="C119" s="1">
         <v>1.4999999999999999E-2</v>
       </c>
-    </row>
-    <row r="120" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D119" s="5" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="120" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A120" s="1">
         <v>31010976</v>
       </c>
       <c r="B120" s="1" t="s">
-        <v>80</v>
+        <v>101</v>
       </c>
       <c r="C120" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="121" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D120" s="5" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="121" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A121" s="1">
         <v>31010977</v>
       </c>
       <c r="B121" s="1" t="s">
-        <v>80</v>
+        <v>101</v>
       </c>
       <c r="C121" s="1">
         <v>1.4999999999999999E-2</v>
       </c>
-    </row>
-    <row r="122" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D121" s="5" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="122" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A122" s="1">
         <v>31029890</v>
       </c>
       <c r="B122" s="1" t="s">
-        <v>80</v>
+        <v>101</v>
       </c>
       <c r="C122" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="123" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D122" s="5" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="123" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A123" s="1">
         <v>10200075</v>
       </c>
       <c r="B123" s="1" t="s">
-        <v>80</v>
+        <v>101</v>
       </c>
       <c r="C123" s="1">
         <v>2</v>
       </c>
-    </row>
-    <row r="124" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D123" s="5" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="124" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A124" s="1">
         <v>10200021</v>
       </c>
       <c r="B124" s="1" t="s">
-        <v>80</v>
+        <v>101</v>
       </c>
       <c r="C124" s="1">
         <v>21.758359527016914</v>
       </c>
-    </row>
-    <row r="125" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D124" s="5" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="125" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A125" s="1">
         <v>10200228</v>
       </c>
       <c r="B125" s="1" t="s">
-        <v>80</v>
+        <v>101</v>
       </c>
       <c r="C125" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="126" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D125" s="5" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="126" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A126" s="1">
         <v>10200023</v>
       </c>
       <c r="B126" s="1" t="s">
-        <v>80</v>
+        <v>101</v>
       </c>
       <c r="C126" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="127" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D126" s="5" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="127" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A127" s="1">
         <v>10200266</v>
       </c>
       <c r="B127" s="1" t="s">
-        <v>80</v>
+        <v>101</v>
       </c>
       <c r="C127" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="128" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D127" s="5" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="128" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A128" s="1">
         <v>10200267</v>
       </c>
       <c r="B128" s="1" t="s">
-        <v>80</v>
+        <v>101</v>
       </c>
       <c r="C128" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="129" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D128" s="5" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="129" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A129" s="1">
         <v>10200265</v>
       </c>
       <c r="B129" s="1" t="s">
-        <v>80</v>
+        <v>101</v>
       </c>
       <c r="C129" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="130" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D129" s="5" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="130" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A130" s="1">
         <v>10200082</v>
       </c>
       <c r="B130" s="1" t="s">
-        <v>80</v>
+        <v>101</v>
       </c>
       <c r="C130" s="1">
         <v>1.2</v>
       </c>
-    </row>
-    <row r="131" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D130" s="5" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="131" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A131" s="1">
         <v>31015345</v>
       </c>
       <c r="B131" s="1" t="s">
-        <v>80</v>
+        <v>101</v>
       </c>
       <c r="C131" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="132" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D131" s="5" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="132" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A132" s="1">
         <v>31010979</v>
       </c>
       <c r="B132" s="1" t="s">
-        <v>80</v>
+        <v>101</v>
       </c>
       <c r="C132" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="133" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D132" s="5" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="133" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A133" s="1">
         <v>31010987</v>
       </c>
       <c r="B133" s="1" t="s">
-        <v>80</v>
+        <v>101</v>
       </c>
       <c r="C133" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="134" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D133" s="5" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="134" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A134" s="1">
         <v>30000527</v>
       </c>
       <c r="B134" s="1" t="s">
-        <v>80</v>
+        <v>101</v>
       </c>
       <c r="C134" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="135" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D134" s="5" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="135" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A135" s="1">
         <v>30000528</v>
       </c>
       <c r="B135" s="1" t="s">
-        <v>80</v>
+        <v>101</v>
       </c>
       <c r="C135" s="1">
         <v>42.5</v>
       </c>
-    </row>
-    <row r="136" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D135" s="5" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="136" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A136" s="1">
         <v>30000517</v>
       </c>
       <c r="B136" s="1" t="s">
-        <v>80</v>
+        <v>101</v>
       </c>
       <c r="C136" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="137" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D136" s="5" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="137" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A137" s="1">
         <v>10200012</v>
       </c>
       <c r="B137" s="1" t="s">
-        <v>81</v>
+        <v>102</v>
       </c>
       <c r="C137" s="1">
         <v>0.7</v>
       </c>
-    </row>
-    <row r="138" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D137" s="5" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="138" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A138" s="1">
         <v>10200093</v>
       </c>
       <c r="B138" s="1" t="s">
-        <v>81</v>
+        <v>102</v>
       </c>
       <c r="C138" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="139" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D138" s="5" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="139" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A139" s="1">
         <v>10200008</v>
       </c>
       <c r="B139" s="1" t="s">
-        <v>81</v>
+        <v>102</v>
       </c>
       <c r="C139" s="1">
         <v>0.8</v>
       </c>
-    </row>
-    <row r="140" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D139" s="5" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="140" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A140" s="1">
         <v>10200005</v>
       </c>
       <c r="B140" s="1" t="s">
-        <v>81</v>
+        <v>102</v>
       </c>
       <c r="C140" s="1">
         <v>5.6753688989784345E-4</v>
       </c>
-    </row>
-    <row r="141" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D140" s="5" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="141" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A141" s="1">
         <v>20000560</v>
       </c>
       <c r="B141" s="1" t="s">
-        <v>81</v>
+        <v>102</v>
       </c>
       <c r="C141" s="1">
         <v>0.52</v>
       </c>
-    </row>
-    <row r="142" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D141" s="5" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="142" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A142" s="1">
         <v>20000579</v>
       </c>
       <c r="B142" s="1" t="s">
-        <v>81</v>
+        <v>102</v>
       </c>
       <c r="C142" s="1">
         <v>2.073525813555175E-2</v>
       </c>
-    </row>
-    <row r="143" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D142" s="5" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="143" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A143" s="1">
         <v>31011665</v>
       </c>
       <c r="B143" s="1" t="s">
-        <v>81</v>
+        <v>102</v>
       </c>
       <c r="C143" s="1">
         <v>5.0000000000000001E-4</v>
       </c>
-    </row>
-    <row r="144" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D143" s="5" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="144" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A144" s="1">
         <v>31011666</v>
       </c>
       <c r="B144" s="1" t="s">
-        <v>81</v>
+        <v>102</v>
       </c>
       <c r="C144" s="1">
         <v>1.4158910401764502E-4</v>
       </c>
-    </row>
-    <row r="145" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D144" s="5" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="145" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A145" s="1">
         <v>10200080</v>
       </c>
       <c r="B145" s="1" t="s">
-        <v>81</v>
+        <v>102</v>
       </c>
       <c r="C145" s="1">
         <v>4.963326712025221E-4</v>
       </c>
-    </row>
-    <row r="146" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D145" s="5" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="146" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A146" s="1">
         <v>10200085</v>
       </c>
       <c r="B146" s="1" t="s">
-        <v>81</v>
+        <v>102</v>
       </c>
       <c r="C146" s="1">
         <v>1.8917896329928116E-4</v>
       </c>
-    </row>
-    <row r="147" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D146" s="5" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="147" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A147" s="1">
         <v>20001578</v>
       </c>
       <c r="B147" s="1" t="s">
-        <v>81</v>
+        <v>102</v>
       </c>
       <c r="C147" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="148" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D147" s="5" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="148" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A148" s="1">
         <v>20000612</v>
       </c>
       <c r="B148" s="1" t="s">
-        <v>81</v>
+        <v>102</v>
       </c>
       <c r="C148" s="1">
         <v>0.02</v>
       </c>
-    </row>
-    <row r="149" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D148" s="5" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="149" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A149" s="1">
         <v>20001668</v>
       </c>
       <c r="B149" s="1" t="s">
-        <v>81</v>
+        <v>102</v>
       </c>
       <c r="C149" s="1">
         <v>0.7</v>
       </c>
-    </row>
-    <row r="150" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D149" s="5" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="150" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A150" s="1">
         <v>20001580</v>
       </c>
       <c r="B150" s="1" t="s">
-        <v>81</v>
+        <v>102</v>
       </c>
       <c r="C150" s="1">
         <v>20.2</v>
       </c>
-    </row>
-    <row r="151" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D150" s="5" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="151" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A151" s="1">
         <v>20001688</v>
       </c>
       <c r="B151" s="1" t="s">
-        <v>81</v>
+        <v>102</v>
       </c>
       <c r="C151" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="152" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D151" s="5" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="152" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A152" s="1">
         <v>20000617</v>
       </c>
       <c r="B152" s="1" t="s">
-        <v>81</v>
+        <v>102</v>
       </c>
       <c r="C152" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="153" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D152" s="5" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="153" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A153" s="1">
         <v>10200189</v>
       </c>
       <c r="B153" s="1" t="s">
-        <v>81</v>
+        <v>102</v>
       </c>
       <c r="C153" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="154" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D153" s="5" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="154" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A154" s="1">
         <v>31013555</v>
       </c>
       <c r="B154" s="1" t="s">
-        <v>81</v>
+        <v>102</v>
       </c>
       <c r="C154" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="155" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D154" s="5" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="155" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A155" s="1">
         <v>10200009</v>
       </c>
       <c r="B155" s="1" t="s">
-        <v>81</v>
+        <v>102</v>
       </c>
       <c r="C155" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="156" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D155" s="5" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="156" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A156" s="1">
         <v>10200227</v>
       </c>
       <c r="B156" s="1" t="s">
-        <v>81</v>
+        <v>102</v>
       </c>
       <c r="C156" s="1">
         <v>0.45</v>
       </c>
-    </row>
-    <row r="157" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D156" s="5" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="157" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A157" s="1">
         <v>10200045</v>
       </c>
       <c r="B157" s="1" t="s">
-        <v>81</v>
+        <v>102</v>
       </c>
       <c r="C157" s="1">
         <v>2.1</v>
       </c>
-    </row>
-    <row r="158" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D157" s="5" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="158" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A158" s="1">
         <v>32004433</v>
       </c>
       <c r="B158" s="1" t="s">
-        <v>81</v>
+        <v>102</v>
       </c>
       <c r="C158" s="1">
         <v>8.854912262577664E-3</v>
       </c>
-    </row>
-    <row r="159" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D158" s="5" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="159" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A159" s="1">
         <v>32004434</v>
       </c>
       <c r="B159" s="1" t="s">
-        <v>81</v>
+        <v>102</v>
       </c>
       <c r="C159" s="1">
         <v>6.641184196933248E-3</v>
       </c>
-    </row>
-    <row r="160" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D159" s="5" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="160" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A160" s="1">
         <v>31010981</v>
       </c>
       <c r="B160" s="1" t="s">
-        <v>81</v>
+        <v>102</v>
       </c>
       <c r="C160" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="161" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D160" s="5" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="161" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A161" s="1">
         <v>31010971</v>
       </c>
       <c r="B161" s="1" t="s">
-        <v>81</v>
+        <v>102</v>
       </c>
       <c r="C161" s="1">
         <v>1.2999999999999999E-2</v>
       </c>
-    </row>
-    <row r="162" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D161" s="5" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="162" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A162" s="1">
         <v>31029889</v>
       </c>
       <c r="B162" s="1" t="s">
-        <v>81</v>
+        <v>102</v>
       </c>
       <c r="C162" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="163" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D162" s="5" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="163" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A163" s="1">
         <v>31010973</v>
       </c>
       <c r="B163" s="1" t="s">
-        <v>81</v>
+        <v>102</v>
       </c>
       <c r="C163" s="1">
         <v>2.5000000000000001E-2</v>
       </c>
-    </row>
-    <row r="164" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D163" s="5" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="164" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A164" s="1">
         <v>31010975</v>
       </c>
       <c r="B164" s="1" t="s">
-        <v>81</v>
+        <v>102</v>
       </c>
       <c r="C164" s="1">
         <v>1.7000000000000001E-2</v>
       </c>
-    </row>
-    <row r="165" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D164" s="5" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="165" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A165" s="1">
         <v>31010976</v>
       </c>
       <c r="B165" s="1" t="s">
-        <v>81</v>
+        <v>102</v>
       </c>
       <c r="C165" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="166" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D165" s="5" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="166" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A166" s="1">
         <v>31010977</v>
       </c>
       <c r="B166" s="1" t="s">
-        <v>81</v>
+        <v>102</v>
       </c>
       <c r="C166" s="1">
         <v>1.4999999999999999E-2</v>
       </c>
-    </row>
-    <row r="167" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D166" s="5" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="167" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A167" s="1">
         <v>31029890</v>
       </c>
       <c r="B167" s="1" t="s">
-        <v>81</v>
+        <v>102</v>
       </c>
       <c r="C167" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="168" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D167" s="5" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="168" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A168" s="1">
         <v>10200075</v>
       </c>
       <c r="B168" s="1" t="s">
-        <v>81</v>
+        <v>102</v>
       </c>
       <c r="C168" s="1">
         <v>0.3</v>
       </c>
-    </row>
-    <row r="169" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D168" s="5" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="169" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A169" s="1">
         <v>10200021</v>
       </c>
       <c r="B169" s="1" t="s">
-        <v>81</v>
+        <v>102</v>
       </c>
       <c r="C169" s="1">
         <v>26</v>
       </c>
-    </row>
-    <row r="170" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D169" s="5" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="170" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A170" s="1">
         <v>10200228</v>
       </c>
       <c r="B170" s="1" t="s">
-        <v>81</v>
+        <v>102</v>
       </c>
       <c r="C170" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="171" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D170" s="5" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="171" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A171" s="1">
         <v>10200023</v>
       </c>
       <c r="B171" s="1" t="s">
-        <v>81</v>
+        <v>102</v>
       </c>
       <c r="C171" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="172" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D171" s="5" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="172" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A172" s="1">
         <v>10200266</v>
       </c>
       <c r="B172" s="1" t="s">
-        <v>81</v>
+        <v>102</v>
       </c>
       <c r="C172" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="173" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D172" s="5" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="173" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A173" s="1">
         <v>10200267</v>
       </c>
       <c r="B173" s="1" t="s">
-        <v>81</v>
+        <v>102</v>
       </c>
       <c r="C173" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="174" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D173" s="5" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="174" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A174" s="1">
         <v>10200265</v>
       </c>
       <c r="B174" s="1" t="s">
-        <v>81</v>
+        <v>102</v>
       </c>
       <c r="C174" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="175" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D174" s="5" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="175" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A175" s="1">
         <v>10200082</v>
       </c>
       <c r="B175" s="1" t="s">
-        <v>81</v>
+        <v>102</v>
       </c>
       <c r="C175" s="1">
         <v>1.31</v>
       </c>
-    </row>
-    <row r="176" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D175" s="5" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="176" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A176" s="1">
         <v>31015345</v>
       </c>
       <c r="B176" s="1" t="s">
-        <v>81</v>
+        <v>102</v>
       </c>
       <c r="C176" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="177" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D176" s="5" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="177" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A177" s="1">
         <v>31010979</v>
       </c>
       <c r="B177" s="1" t="s">
-        <v>81</v>
+        <v>102</v>
       </c>
       <c r="C177" s="1">
         <v>4.4999999999999998E-2</v>
       </c>
-    </row>
-    <row r="178" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D177" s="5" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="178" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A178" s="1">
         <v>31010987</v>
       </c>
       <c r="B178" s="1" t="s">
-        <v>81</v>
+        <v>102</v>
       </c>
       <c r="C178" s="1">
         <v>2.4E-2</v>
       </c>
-    </row>
-    <row r="179" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D178" s="5" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="179" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A179" s="1">
         <v>30000527</v>
       </c>
       <c r="B179" s="1" t="s">
-        <v>81</v>
+        <v>102</v>
       </c>
       <c r="C179" s="1">
         <v>0.7</v>
       </c>
-    </row>
-    <row r="180" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D179" s="5" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="180" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A180" s="1">
         <v>30000528</v>
       </c>
       <c r="B180" s="1" t="s">
-        <v>81</v>
+        <v>102</v>
       </c>
       <c r="C180" s="1">
         <v>42</v>
       </c>
-    </row>
-    <row r="181" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D180" s="5" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="181" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A181" s="1">
         <v>30000517</v>
       </c>
       <c r="B181" s="1" t="s">
-        <v>81</v>
+        <v>102</v>
       </c>
       <c r="C181" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="182" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D181" s="5" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="182" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A182" s="1">
         <v>10200012</v>
       </c>
       <c r="B182" s="1" t="s">
-        <v>82</v>
+        <v>103</v>
       </c>
       <c r="C182" s="1">
         <v>0.7</v>
       </c>
-    </row>
-    <row r="183" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D182" s="5" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="183" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A183" s="1">
         <v>10200093</v>
       </c>
       <c r="B183" s="1" t="s">
-        <v>82</v>
+        <v>103</v>
       </c>
       <c r="C183" s="1">
         <v>4.5</v>
       </c>
-    </row>
-    <row r="184" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D183" s="5" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="184" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A184" s="1">
         <v>10200008</v>
       </c>
       <c r="B184" s="1" t="s">
-        <v>82</v>
+        <v>103</v>
       </c>
       <c r="C184" s="1">
         <v>0.8</v>
       </c>
-    </row>
-    <row r="185" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D184" s="5" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="185" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A185" s="1">
         <v>10200005</v>
       </c>
       <c r="B185" s="1" t="s">
-        <v>82</v>
+        <v>103</v>
       </c>
       <c r="C185" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="186" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D185" s="5" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="186" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A186" s="1">
         <v>20000560</v>
       </c>
       <c r="B186" s="1" t="s">
-        <v>82</v>
+        <v>103</v>
       </c>
       <c r="C186" s="1">
         <v>0.51</v>
       </c>
-    </row>
-    <row r="187" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D186" s="5" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="187" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A187" s="1">
         <v>20000579</v>
       </c>
       <c r="B187" s="1" t="s">
-        <v>82</v>
+        <v>103</v>
       </c>
       <c r="C187" s="1">
         <v>2.073525813555175E-2</v>
       </c>
-    </row>
-    <row r="188" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D187" s="5" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="188" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A188" s="1">
         <v>31011665</v>
       </c>
       <c r="B188" s="1" t="s">
-        <v>82</v>
+        <v>103</v>
       </c>
       <c r="C188" s="1">
         <v>1.5E-3</v>
       </c>
-    </row>
-    <row r="189" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D188" s="5" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="189" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A189" s="1">
         <v>31011666</v>
       </c>
       <c r="B189" s="1" t="s">
-        <v>82</v>
+        <v>103</v>
       </c>
       <c r="C189" s="1">
         <v>1.5790046509546322E-4</v>
       </c>
-    </row>
-    <row r="190" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D189" s="5" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="190" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A190" s="1">
         <v>10200080</v>
       </c>
       <c r="B190" s="1" t="s">
-        <v>82</v>
+        <v>103</v>
       </c>
       <c r="C190" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="191" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D190" s="5" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="191" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A191" s="1">
         <v>10200085</v>
       </c>
       <c r="B191" s="1" t="s">
-        <v>82</v>
+        <v>103</v>
       </c>
       <c r="C191" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="192" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D191" s="5" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="192" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A192" s="1">
         <v>20001578</v>
       </c>
       <c r="B192" s="1" t="s">
-        <v>82</v>
+        <v>103</v>
       </c>
       <c r="C192" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="193" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D192" s="5" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="193" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A193" s="1">
         <v>20000612</v>
       </c>
       <c r="B193" s="1" t="s">
-        <v>82</v>
+        <v>103</v>
       </c>
       <c r="C193" s="1">
         <v>0.02</v>
       </c>
-    </row>
-    <row r="194" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D193" s="5" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="194" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A194" s="1">
         <v>20001668</v>
       </c>
       <c r="B194" s="1" t="s">
-        <v>82</v>
+        <v>103</v>
       </c>
       <c r="C194" s="1">
         <v>1.1251676563163464</v>
       </c>
-    </row>
-    <row r="195" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D194" s="5" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="195" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A195" s="1">
         <v>20001580</v>
       </c>
       <c r="B195" s="1" t="s">
-        <v>82</v>
+        <v>103</v>
       </c>
       <c r="C195" s="1">
         <v>20.2</v>
       </c>
-    </row>
-    <row r="196" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D195" s="5" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="196" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A196" s="1">
         <v>20001688</v>
       </c>
       <c r="B196" s="1" t="s">
-        <v>82</v>
+        <v>103</v>
       </c>
       <c r="C196" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="197" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D196" s="5" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="197" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A197" s="1">
         <v>20000617</v>
       </c>
       <c r="B197" s="1" t="s">
-        <v>82</v>
+        <v>103</v>
       </c>
       <c r="C197" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="198" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D197" s="5" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="198" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A198" s="1">
         <v>10200189</v>
       </c>
       <c r="B198" s="1" t="s">
-        <v>82</v>
+        <v>103</v>
       </c>
       <c r="C198" s="1">
         <v>0.25</v>
       </c>
-    </row>
-    <row r="199" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D198" s="5" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="199" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A199" s="1">
         <v>31013555</v>
       </c>
       <c r="B199" s="1" t="s">
-        <v>82</v>
+        <v>103</v>
       </c>
       <c r="C199" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="200" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D199" s="5" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="200" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A200" s="1">
         <v>10200009</v>
       </c>
       <c r="B200" s="1" t="s">
-        <v>82</v>
+        <v>103</v>
       </c>
       <c r="C200" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="201" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D200" s="5" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="201" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A201" s="1">
         <v>10200227</v>
       </c>
       <c r="B201" s="1" t="s">
-        <v>82</v>
+        <v>103</v>
       </c>
       <c r="C201" s="1">
         <v>0.45</v>
       </c>
-    </row>
-    <row r="202" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D201" s="5" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="202" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A202" s="1">
         <v>10200045</v>
       </c>
       <c r="B202" s="1" t="s">
-        <v>82</v>
+        <v>103</v>
       </c>
       <c r="C202" s="1">
         <v>2.1</v>
       </c>
-    </row>
-    <row r="203" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D202" s="5" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="203" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A203" s="1">
         <v>32004433</v>
       </c>
       <c r="B203" s="1" t="s">
-        <v>82</v>
+        <v>103</v>
       </c>
       <c r="C203" s="1">
         <v>5.8661921569010877E-3</v>
       </c>
-    </row>
-    <row r="204" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D203" s="5" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="204" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A204" s="1">
         <v>32004434</v>
       </c>
       <c r="B204" s="1" t="s">
-        <v>82</v>
+        <v>103</v>
       </c>
       <c r="C204" s="1">
         <v>1.6E-2</v>
       </c>
-    </row>
-    <row r="205" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D204" s="5" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="205" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A205" s="1">
         <v>31010981</v>
       </c>
       <c r="B205" s="1" t="s">
-        <v>82</v>
+        <v>103</v>
       </c>
       <c r="C205" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="206" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D205" s="5" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="206" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A206" s="1">
         <v>31010971</v>
       </c>
       <c r="B206" s="1" t="s">
-        <v>82</v>
+        <v>103</v>
       </c>
       <c r="C206" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="207" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D206" s="5" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="207" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A207" s="1">
         <v>31029889</v>
       </c>
       <c r="B207" s="1" t="s">
-        <v>82</v>
+        <v>103</v>
       </c>
       <c r="C207" s="1">
         <v>0.01</v>
       </c>
-    </row>
-    <row r="208" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D207" s="5" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="208" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A208" s="1">
         <v>31010973</v>
       </c>
       <c r="B208" s="1" t="s">
-        <v>82</v>
+        <v>103</v>
       </c>
       <c r="C208" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="209" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D208" s="5" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="209" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A209" s="1">
         <v>31010975</v>
       </c>
       <c r="B209" s="1" t="s">
-        <v>82</v>
+        <v>103</v>
       </c>
       <c r="C209" s="1">
         <v>6.9576534187606367E-3</v>
       </c>
-    </row>
-    <row r="210" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D209" s="5" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="210" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A210" s="1">
         <v>31010976</v>
       </c>
       <c r="B210" s="1" t="s">
-        <v>82</v>
+        <v>103</v>
       </c>
       <c r="C210" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="211" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D210" s="5" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="211" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A211" s="1">
         <v>31010977</v>
       </c>
       <c r="B211" s="1" t="s">
-        <v>82</v>
+        <v>103</v>
       </c>
       <c r="C211" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="212" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D211" s="5" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="212" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A212" s="1">
         <v>31029890</v>
       </c>
       <c r="B212" s="1" t="s">
-        <v>82</v>
+        <v>103</v>
       </c>
       <c r="C212" s="1">
         <v>5.3790914714504732E-3</v>
       </c>
-    </row>
-    <row r="213" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D212" s="5" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="213" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A213" s="1">
         <v>10200075</v>
       </c>
       <c r="B213" s="1" t="s">
-        <v>82</v>
+        <v>103</v>
       </c>
       <c r="C213" s="1">
         <v>0.3</v>
       </c>
-    </row>
-    <row r="214" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D213" s="5" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="214" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A214" s="1">
         <v>10200021</v>
       </c>
       <c r="B214" s="1" t="s">
-        <v>82</v>
+        <v>103</v>
       </c>
       <c r="C214" s="1">
         <v>24</v>
       </c>
-    </row>
-    <row r="215" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D214" s="5" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="215" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A215" s="1">
         <v>10200228</v>
       </c>
       <c r="B215" s="1" t="s">
-        <v>82</v>
+        <v>103</v>
       </c>
       <c r="C215" s="1">
         <v>7</v>
       </c>
-    </row>
-    <row r="216" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D215" s="5" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="216" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A216" s="1">
         <v>10200023</v>
       </c>
       <c r="B216" s="1" t="s">
-        <v>82</v>
+        <v>103</v>
       </c>
       <c r="C216" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="217" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D216" s="5" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="217" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A217" s="1">
         <v>10200266</v>
       </c>
       <c r="B217" s="1" t="s">
-        <v>82</v>
+        <v>103</v>
       </c>
       <c r="C217" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="218" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D217" s="5" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="218" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A218" s="1">
         <v>10200267</v>
       </c>
       <c r="B218" s="1" t="s">
-        <v>82</v>
+        <v>103</v>
       </c>
       <c r="C218" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="219" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D218" s="5" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="219" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A219" s="1">
         <v>10200265</v>
       </c>
       <c r="B219" s="1" t="s">
-        <v>82</v>
+        <v>103</v>
       </c>
       <c r="C219" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="220" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D219" s="5" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="220" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A220" s="1">
         <v>10200082</v>
       </c>
       <c r="B220" s="1" t="s">
-        <v>82</v>
+        <v>103</v>
       </c>
       <c r="C220" s="1">
         <v>1.5</v>
       </c>
-    </row>
-    <row r="221" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D220" s="5" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="221" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A221" s="1">
         <v>31015345</v>
       </c>
       <c r="B221" s="1" t="s">
-        <v>82</v>
+        <v>103</v>
       </c>
       <c r="C221" s="1">
         <v>0.6</v>
       </c>
-    </row>
-    <row r="222" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D221" s="5" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="222" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A222" s="1">
         <v>31010979</v>
       </c>
       <c r="B222" s="1" t="s">
-        <v>82</v>
+        <v>103</v>
       </c>
       <c r="C222" s="1">
         <v>0.02</v>
       </c>
-    </row>
-    <row r="223" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D222" s="5" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="223" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A223" s="1">
         <v>31010987</v>
       </c>
       <c r="B223" s="1" t="s">
-        <v>82</v>
+        <v>103</v>
       </c>
       <c r="C223" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="224" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D223" s="5" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="224" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A224" s="1">
         <v>30000527</v>
       </c>
       <c r="B224" s="1" t="s">
-        <v>82</v>
+        <v>103</v>
       </c>
       <c r="C224" s="1">
         <v>0.7</v>
       </c>
-    </row>
-    <row r="225" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D224" s="5" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="225" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A225" s="1">
         <v>30000528</v>
       </c>
       <c r="B225" s="1" t="s">
-        <v>82</v>
+        <v>103</v>
       </c>
       <c r="C225" s="1">
         <v>43.5</v>
       </c>
-    </row>
-    <row r="226" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D225" s="5" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="226" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A226" s="1">
         <v>30000517</v>
       </c>
       <c r="B226" s="1" t="s">
-        <v>82</v>
+        <v>103</v>
       </c>
       <c r="C226" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="227" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D226" s="5" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="227" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A227" s="1">
         <v>10200012</v>
       </c>
       <c r="B227" s="1" t="s">
-        <v>83</v>
+        <v>104</v>
       </c>
       <c r="C227" s="1">
         <v>0.7</v>
       </c>
-    </row>
-    <row r="228" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D227" s="5" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="228" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A228" s="1">
         <v>10200093</v>
       </c>
       <c r="B228" s="1" t="s">
-        <v>83</v>
+        <v>104</v>
       </c>
       <c r="C228" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="229" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D228" s="5" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="229" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A229" s="1">
         <v>10200008</v>
       </c>
       <c r="B229" s="1" t="s">
-        <v>83</v>
+        <v>104</v>
       </c>
       <c r="C229" s="1">
         <v>0.8</v>
       </c>
-    </row>
-    <row r="230" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D229" s="5" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="230" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A230" s="1">
         <v>10200005</v>
       </c>
       <c r="B230" s="1" t="s">
-        <v>83</v>
+        <v>104</v>
       </c>
       <c r="C230" s="1">
         <v>1.4E-3</v>
       </c>
-    </row>
-    <row r="231" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D230" s="5" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="231" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A231" s="1">
         <v>20000560</v>
       </c>
       <c r="B231" s="1" t="s">
-        <v>83</v>
+        <v>104</v>
       </c>
       <c r="C231" s="1">
         <v>0.51</v>
       </c>
-    </row>
-    <row r="232" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D231" s="5" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="232" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A232" s="1">
         <v>20000579</v>
       </c>
       <c r="B232" s="1" t="s">
-        <v>83</v>
+        <v>104</v>
       </c>
       <c r="C232" s="1">
         <v>2.073525813555175E-2</v>
       </c>
-    </row>
-    <row r="233" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D232" s="5" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="233" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A233" s="1">
         <v>31011665</v>
       </c>
       <c r="B233" s="1" t="s">
-        <v>83</v>
+        <v>104</v>
       </c>
       <c r="C233" s="1">
         <v>4.4875979112271542E-4</v>
       </c>
-    </row>
-    <row r="234" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D233" s="5" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="234" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A234" s="1">
         <v>31011666</v>
       </c>
       <c r="B234" s="1" t="s">
-        <v>83</v>
+        <v>104</v>
       </c>
       <c r="C234" s="1">
         <v>8.1592689295039166E-5</v>
       </c>
-    </row>
-    <row r="235" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D234" s="5" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="235" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A235" s="1">
         <v>10200080</v>
       </c>
       <c r="B235" s="1" t="s">
-        <v>83</v>
+        <v>104</v>
       </c>
       <c r="C235" s="1">
         <v>3.6716710182767623E-4</v>
       </c>
-    </row>
-    <row r="236" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D235" s="5" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="236" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A236" s="1">
         <v>10200085</v>
       </c>
       <c r="B236" s="1" t="s">
-        <v>83</v>
+        <v>104</v>
       </c>
       <c r="C236" s="1">
         <v>4.2836161879895564E-4</v>
       </c>
-    </row>
-    <row r="237" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D236" s="5" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="237" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A237" s="1">
         <v>20001578</v>
       </c>
       <c r="B237" s="1" t="s">
-        <v>83</v>
+        <v>104</v>
       </c>
       <c r="C237" s="1">
         <v>20.2</v>
       </c>
-    </row>
-    <row r="238" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D237" s="5" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="238" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A238" s="1">
         <v>20000612</v>
       </c>
       <c r="B238" s="1" t="s">
-        <v>83</v>
+        <v>104</v>
       </c>
       <c r="C238" s="1">
         <v>0.02</v>
       </c>
-    </row>
-    <row r="239" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D238" s="5" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="239" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A239" s="1">
         <v>20001668</v>
       </c>
       <c r="B239" s="1" t="s">
-        <v>83</v>
+        <v>104</v>
       </c>
       <c r="C239" s="1">
         <v>0.51760645765091251</v>
       </c>
-    </row>
-    <row r="240" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D239" s="5" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="240" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A240" s="1">
         <v>20001580</v>
       </c>
       <c r="B240" s="1" t="s">
-        <v>83</v>
+        <v>104</v>
       </c>
       <c r="C240" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="241" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D240" s="5" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="241" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A241" s="1">
         <v>20001688</v>
       </c>
       <c r="B241" s="1" t="s">
-        <v>83</v>
+        <v>104</v>
       </c>
       <c r="C241" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="242" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D241" s="5" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="242" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A242" s="1">
         <v>20000617</v>
       </c>
       <c r="B242" s="1" t="s">
-        <v>83</v>
+        <v>104</v>
       </c>
       <c r="C242" s="1">
         <v>3.3371409921671015E-2</v>
       </c>
-    </row>
-    <row r="243" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D242" s="5" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="243" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A243" s="1">
         <v>10200189</v>
       </c>
       <c r="B243" s="1" t="s">
-        <v>83</v>
+        <v>104</v>
       </c>
       <c r="C243" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="244" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D243" s="5" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="244" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A244" s="1">
         <v>31013555</v>
       </c>
       <c r="B244" s="1" t="s">
-        <v>83</v>
+        <v>104</v>
       </c>
       <c r="C244" s="1">
         <v>1.8732284434950499</v>
       </c>
-    </row>
-    <row r="245" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D244" s="5" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="245" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A245" s="1">
         <v>10200009</v>
       </c>
       <c r="B245" s="1" t="s">
-        <v>83</v>
+        <v>104</v>
       </c>
       <c r="C245" s="1">
         <v>0.5</v>
       </c>
-    </row>
-    <row r="246" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D245" s="5" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="246" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A246" s="1">
         <v>10200227</v>
       </c>
       <c r="B246" s="1" t="s">
-        <v>83</v>
+        <v>104</v>
       </c>
       <c r="C246" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="247" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D246" s="5" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="247" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A247" s="1">
         <v>10200045</v>
       </c>
       <c r="B247" s="1" t="s">
-        <v>83</v>
+        <v>104</v>
       </c>
       <c r="C247" s="1">
         <v>1.5181720090531081</v>
       </c>
-    </row>
-    <row r="248" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D247" s="5" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="248" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A248" s="1">
         <v>32004433</v>
       </c>
       <c r="B248" s="1" t="s">
-        <v>83</v>
+        <v>104</v>
       </c>
       <c r="C248" s="1">
         <v>5.8661921569010877E-3</v>
       </c>
-    </row>
-    <row r="249" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D248" s="5" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="249" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A249" s="1">
         <v>32004434</v>
       </c>
       <c r="B249" s="1" t="s">
-        <v>83</v>
+        <v>104</v>
       </c>
       <c r="C249" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="250" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D249" s="5" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="250" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A250" s="1">
         <v>31010981</v>
       </c>
       <c r="B250" s="1" t="s">
-        <v>83</v>
+        <v>104</v>
       </c>
       <c r="C250" s="1">
         <v>0.03</v>
       </c>
-    </row>
-    <row r="251" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D250" s="5" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="251" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A251" s="1">
         <v>31010971</v>
       </c>
       <c r="B251" s="1" t="s">
-        <v>83</v>
+        <v>104</v>
       </c>
       <c r="C251" s="1">
         <v>8.9999999999999993E-3</v>
       </c>
-    </row>
-    <row r="252" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D251" s="5" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="252" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A252" s="1">
         <v>31029889</v>
       </c>
       <c r="B252" s="1" t="s">
-        <v>83</v>
+        <v>104</v>
       </c>
       <c r="C252" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="253" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D252" s="5" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="253" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A253" s="1">
         <v>31010973</v>
       </c>
       <c r="B253" s="1" t="s">
-        <v>83</v>
+        <v>104</v>
       </c>
       <c r="C253" s="1">
         <v>1.3054830287206266E-2</v>
       </c>
-    </row>
-    <row r="254" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D253" s="5" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="254" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A254" s="1">
         <v>31010975</v>
       </c>
       <c r="B254" s="1" t="s">
-        <v>83</v>
+        <v>104</v>
       </c>
       <c r="C254" s="1">
         <v>8.9999999999999993E-3</v>
       </c>
-    </row>
-    <row r="255" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D254" s="5" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="255" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A255" s="1">
         <v>31010976</v>
       </c>
       <c r="B255" s="1" t="s">
-        <v>83</v>
+        <v>104</v>
       </c>
       <c r="C255" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="256" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D255" s="5" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="256" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A256" s="1">
         <v>31010977</v>
       </c>
       <c r="B256" s="1" t="s">
-        <v>83</v>
+        <v>104</v>
       </c>
       <c r="C256" s="1">
         <v>8.9999999999999993E-3</v>
       </c>
-    </row>
-    <row r="257" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D256" s="5" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="257" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A257" s="1">
         <v>31029890</v>
       </c>
       <c r="B257" s="1" t="s">
-        <v>83</v>
+        <v>104</v>
       </c>
       <c r="C257" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="258" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D257" s="5" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="258" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A258" s="1">
         <v>10200075</v>
       </c>
       <c r="B258" s="1" t="s">
-        <v>83</v>
+        <v>104</v>
       </c>
       <c r="C258" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="259" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D258" s="5" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="259" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A259" s="1">
         <v>10200021</v>
       </c>
       <c r="B259" s="1" t="s">
-        <v>83</v>
+        <v>104</v>
       </c>
       <c r="C259" s="1">
         <v>4.5</v>
       </c>
-    </row>
-    <row r="260" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D259" s="5" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="260" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A260" s="1">
         <v>10200228</v>
       </c>
       <c r="B260" s="1" t="s">
-        <v>83</v>
+        <v>104</v>
       </c>
       <c r="C260" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="261" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D260" s="5" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="261" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A261" s="1">
         <v>10200023</v>
       </c>
       <c r="B261" s="1" t="s">
-        <v>83</v>
+        <v>104</v>
       </c>
       <c r="C261" s="1">
         <v>30</v>
       </c>
-    </row>
-    <row r="262" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D261" s="5" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="262" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A262" s="1">
         <v>10200266</v>
       </c>
       <c r="B262" s="1" t="s">
-        <v>83</v>
+        <v>104</v>
       </c>
       <c r="C262" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="263" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D262" s="5" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="263" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A263" s="1">
         <v>10200267</v>
       </c>
       <c r="B263" s="1" t="s">
-        <v>83</v>
+        <v>104</v>
       </c>
       <c r="C263" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="264" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D263" s="5" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="264" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A264" s="1">
         <v>10200265</v>
       </c>
       <c r="B264" s="1" t="s">
-        <v>83</v>
+        <v>104</v>
       </c>
       <c r="C264" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="265" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D264" s="5" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="265" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A265" s="1">
         <v>10200082</v>
       </c>
       <c r="B265" s="1" t="s">
-        <v>83</v>
+        <v>104</v>
       </c>
       <c r="C265" s="1">
         <v>1.52</v>
       </c>
-    </row>
-    <row r="266" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D265" s="5" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="266" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A266" s="1">
         <v>31015345</v>
       </c>
       <c r="B266" s="1" t="s">
-        <v>83</v>
+        <v>104</v>
       </c>
       <c r="C266" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="267" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D266" s="5" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="267" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A267" s="1">
         <v>31010979</v>
       </c>
       <c r="B267" s="1" t="s">
-        <v>83</v>
+        <v>104</v>
       </c>
       <c r="C267" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="268" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D267" s="5" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="268" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A268" s="1">
         <v>31010987</v>
       </c>
       <c r="B268" s="1" t="s">
-        <v>83</v>
+        <v>104</v>
       </c>
       <c r="C268" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="269" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D268" s="5" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="269" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A269" s="1">
         <v>30000527</v>
       </c>
       <c r="B269" s="1" t="s">
-        <v>83</v>
+        <v>104</v>
       </c>
       <c r="C269" s="1">
         <v>0.53</v>
       </c>
-    </row>
-    <row r="270" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D269" s="5" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="270" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A270" s="1">
         <v>30000528</v>
       </c>
       <c r="B270" s="1" t="s">
-        <v>83</v>
+        <v>104</v>
       </c>
       <c r="C270" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="271" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D270" s="5" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="271" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A271" s="1">
         <v>30000517</v>
       </c>
       <c r="B271" s="1" t="s">
-        <v>83</v>
+        <v>104</v>
       </c>
       <c r="C271" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="272" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D271" s="5" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="272" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A272" s="1">
         <v>10200012</v>
       </c>
       <c r="B272" s="1" t="s">
-        <v>84</v>
+        <v>105</v>
       </c>
       <c r="C272" s="1">
         <v>0.7</v>
       </c>
-    </row>
-    <row r="273" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D272" s="5" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="273" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A273" s="1">
         <v>10200093</v>
       </c>
       <c r="B273" s="1" t="s">
-        <v>84</v>
+        <v>105</v>
       </c>
       <c r="C273" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="274" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D273" s="5" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="274" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A274" s="1">
         <v>10200008</v>
       </c>
       <c r="B274" s="1" t="s">
-        <v>84</v>
+        <v>105</v>
       </c>
       <c r="C274" s="1">
         <v>0.3</v>
       </c>
-    </row>
-    <row r="275" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D274" s="5" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="275" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A275" s="1">
         <v>10200005</v>
       </c>
       <c r="B275" s="1" t="s">
-        <v>84</v>
+        <v>105</v>
       </c>
       <c r="C275" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="276" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D275" s="5" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="276" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A276" s="1">
         <v>20000560</v>
       </c>
       <c r="B276" s="1" t="s">
-        <v>84</v>
+        <v>105</v>
       </c>
       <c r="C276" s="1">
         <v>0.52500000000000002</v>
       </c>
-    </row>
-    <row r="277" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D276" s="5" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="277" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A277" s="1">
         <v>20000579</v>
       </c>
       <c r="B277" s="1" t="s">
-        <v>84</v>
+        <v>105</v>
       </c>
       <c r="C277" s="1">
         <v>2.073525813555175E-2</v>
       </c>
-    </row>
-    <row r="278" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D277" s="5" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="278" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A278" s="1">
         <v>31011665</v>
       </c>
       <c r="B278" s="1" t="s">
-        <v>84</v>
+        <v>105</v>
       </c>
       <c r="C278" s="1">
         <v>1E-3</v>
       </c>
-    </row>
-    <row r="279" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D278" s="5" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="279" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A279" s="1">
         <v>31011666</v>
       </c>
       <c r="B279" s="1" t="s">
-        <v>84</v>
+        <v>105</v>
       </c>
       <c r="C279" s="1">
         <v>3.2718996791308565E-4</v>
       </c>
-    </row>
-    <row r="280" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D279" s="5" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="280" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A280" s="1">
         <v>10200080</v>
       </c>
       <c r="B280" s="1" t="s">
-        <v>84</v>
+        <v>105</v>
       </c>
       <c r="C280" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="281" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D280" s="5" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="281" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A281" s="1">
         <v>10200085</v>
       </c>
       <c r="B281" s="1" t="s">
-        <v>84</v>
+        <v>105</v>
       </c>
       <c r="C281" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="282" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D281" s="5" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="282" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A282" s="1">
         <v>20001578</v>
       </c>
       <c r="B282" s="1" t="s">
-        <v>84</v>
+        <v>105</v>
       </c>
       <c r="C282" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="283" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D282" s="5" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="283" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A283" s="1">
         <v>20000612</v>
       </c>
       <c r="B283" s="1" t="s">
-        <v>84</v>
+        <v>105</v>
       </c>
       <c r="C283" s="1">
         <v>0.02</v>
       </c>
-    </row>
-    <row r="284" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D283" s="5" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="284" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A284" s="1">
         <v>20001668</v>
       </c>
       <c r="B284" s="1" t="s">
-        <v>84</v>
+        <v>105</v>
       </c>
       <c r="C284" s="1">
         <v>1.2319269443145699</v>
       </c>
-    </row>
-    <row r="285" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D284" s="5" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="285" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A285" s="1">
         <v>20001580</v>
       </c>
       <c r="B285" s="1" t="s">
-        <v>84</v>
+        <v>105</v>
       </c>
       <c r="C285" s="1">
         <v>20.2</v>
       </c>
-    </row>
-    <row r="286" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D285" s="5" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="286" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A286" s="1">
         <v>20001688</v>
       </c>
       <c r="B286" s="1" t="s">
-        <v>84</v>
+        <v>105</v>
       </c>
       <c r="C286" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="287" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D286" s="5" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="287" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A287" s="1">
         <v>20000617</v>
       </c>
       <c r="B287" s="1" t="s">
-        <v>84</v>
+        <v>105</v>
       </c>
       <c r="C287" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="288" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D287" s="5" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="288" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A288" s="1">
         <v>10200189</v>
       </c>
       <c r="B288" s="1" t="s">
-        <v>84</v>
+        <v>105</v>
       </c>
       <c r="C288" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="289" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D288" s="5" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="289" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A289" s="1">
         <v>31013555</v>
       </c>
       <c r="B289" s="1" t="s">
-        <v>84</v>
+        <v>105</v>
       </c>
       <c r="C289" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="290" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D289" s="5" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="290" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A290" s="1">
         <v>10200009</v>
       </c>
       <c r="B290" s="1" t="s">
-        <v>84</v>
+        <v>105</v>
       </c>
       <c r="C290" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="291" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D290" s="5" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="291" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A291" s="1">
         <v>10200227</v>
       </c>
       <c r="B291" s="1" t="s">
-        <v>84</v>
+        <v>105</v>
       </c>
       <c r="C291" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="292" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D291" s="5" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="292" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A292" s="1">
         <v>10200045</v>
       </c>
       <c r="B292" s="1" t="s">
-        <v>84</v>
+        <v>105</v>
       </c>
       <c r="C292" s="1">
         <v>2.4</v>
       </c>
-    </row>
-    <row r="293" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D292" s="5" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="293" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A293" s="1">
         <v>32004433</v>
       </c>
       <c r="B293" s="1" t="s">
-        <v>84</v>
+        <v>105</v>
       </c>
       <c r="C293" s="1">
         <v>5.8661921569010877E-3</v>
       </c>
-    </row>
-    <row r="294" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D293" s="5" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="294" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A294" s="1">
         <v>32004434</v>
       </c>
       <c r="B294" s="1" t="s">
-        <v>84</v>
+        <v>105</v>
       </c>
       <c r="C294" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="295" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D294" s="5" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="295" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A295" s="1">
         <v>31010981</v>
       </c>
       <c r="B295" s="1" t="s">
-        <v>84</v>
+        <v>105</v>
       </c>
       <c r="C295" s="1">
         <v>0.23764867184107119</v>
       </c>
-    </row>
-    <row r="296" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D295" s="5" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="296" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A296" s="1">
         <v>31010971</v>
       </c>
       <c r="B296" s="1" t="s">
-        <v>84</v>
+        <v>105</v>
       </c>
       <c r="C296" s="1">
         <v>0.02</v>
       </c>
-    </row>
-    <row r="297" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D296" s="5" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="297" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A297" s="1">
         <v>31029889</v>
       </c>
       <c r="B297" s="1" t="s">
-        <v>84</v>
+        <v>105</v>
       </c>
       <c r="C297" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="298" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D297" s="5" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="298" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A298" s="1">
         <v>31010973</v>
       </c>
       <c r="B298" s="1" t="s">
-        <v>84</v>
+        <v>105</v>
       </c>
       <c r="C298" s="1">
         <v>3.5000000000000003E-2</v>
       </c>
-    </row>
-    <row r="299" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D298" s="5" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="299" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A299" s="1">
         <v>31010975</v>
       </c>
       <c r="B299" s="1" t="s">
-        <v>84</v>
+        <v>105</v>
       </c>
       <c r="C299" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="300" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D299" s="5" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="300" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A300" s="1">
         <v>31010976</v>
       </c>
       <c r="B300" s="1" t="s">
-        <v>84</v>
+        <v>105</v>
       </c>
       <c r="C300" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="301" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D300" s="5" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="301" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A301" s="1">
         <v>31010977</v>
       </c>
       <c r="B301" s="1" t="s">
-        <v>84</v>
+        <v>105</v>
       </c>
       <c r="C301" s="1">
         <v>1.1999640010799676E-2</v>
       </c>
-    </row>
-    <row r="302" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D301" s="5" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="302" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A302" s="1">
         <v>31029890</v>
       </c>
       <c r="B302" s="1" t="s">
-        <v>84</v>
+        <v>105</v>
       </c>
       <c r="C302" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="303" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D302" s="5" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="303" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A303" s="1">
         <v>10200075</v>
       </c>
       <c r="B303" s="1" t="s">
-        <v>84</v>
+        <v>105</v>
       </c>
       <c r="C303" s="1">
         <v>0.26</v>
       </c>
-    </row>
-    <row r="304" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D303" s="5" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="304" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A304" s="1">
         <v>10200021</v>
       </c>
       <c r="B304" s="1" t="s">
-        <v>84</v>
+        <v>105</v>
       </c>
       <c r="C304" s="1">
         <v>24</v>
       </c>
-    </row>
-    <row r="305" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D304" s="5" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="305" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A305" s="1">
         <v>10200228</v>
       </c>
       <c r="B305" s="1" t="s">
-        <v>84</v>
+        <v>105</v>
       </c>
       <c r="C305" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="306" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D305" s="5" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="306" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A306" s="1">
         <v>10200023</v>
       </c>
       <c r="B306" s="1" t="s">
-        <v>84</v>
+        <v>105</v>
       </c>
       <c r="C306" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="307" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D306" s="5" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="307" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A307" s="1">
         <v>10200266</v>
       </c>
       <c r="B307" s="1" t="s">
-        <v>84</v>
+        <v>105</v>
       </c>
       <c r="C307" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="308" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D307" s="5" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="308" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A308" s="1">
         <v>10200267</v>
       </c>
       <c r="B308" s="1" t="s">
-        <v>84</v>
+        <v>105</v>
       </c>
       <c r="C308" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="309" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D308" s="5" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="309" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A309" s="1">
         <v>10200265</v>
       </c>
       <c r="B309" s="1" t="s">
-        <v>84</v>
+        <v>105</v>
       </c>
       <c r="C309" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="310" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D309" s="5" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="310" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A310" s="1">
         <v>10200082</v>
       </c>
       <c r="B310" s="1" t="s">
-        <v>84</v>
+        <v>105</v>
       </c>
       <c r="C310" s="1">
         <v>1.55</v>
       </c>
-    </row>
-    <row r="311" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D310" s="5" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="311" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A311" s="1">
         <v>31015345</v>
       </c>
       <c r="B311" s="1" t="s">
-        <v>84</v>
+        <v>105</v>
       </c>
       <c r="C311" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="312" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D311" s="5" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="312" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A312" s="1">
         <v>31010979</v>
       </c>
       <c r="B312" s="1" t="s">
-        <v>84</v>
+        <v>105</v>
       </c>
       <c r="C312" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="313" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D312" s="5" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="313" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A313" s="1">
         <v>31010987</v>
       </c>
       <c r="B313" s="1" t="s">
-        <v>84</v>
+        <v>105</v>
       </c>
       <c r="C313" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="314" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D313" s="5" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="314" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A314" s="1">
         <v>30000527</v>
       </c>
       <c r="B314" s="1" t="s">
-        <v>84</v>
+        <v>105</v>
       </c>
       <c r="C314" s="1">
         <v>0.7</v>
       </c>
-    </row>
-    <row r="315" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D314" s="5" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="315" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A315" s="1">
         <v>30000528</v>
       </c>
       <c r="B315" s="1" t="s">
-        <v>84</v>
+        <v>105</v>
       </c>
       <c r="C315" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="316" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D315" s="5" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="316" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A316" s="1">
         <v>30000517</v>
       </c>
       <c r="B316" s="1" t="s">
-        <v>84</v>
+        <v>105</v>
       </c>
       <c r="C316" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="317" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D316" s="5" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="317" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A317" s="1">
         <v>10200012</v>
       </c>
       <c r="B317" s="1" t="s">
-        <v>85</v>
+        <v>106</v>
       </c>
       <c r="C317" s="1">
         <v>0.7</v>
       </c>
-    </row>
-    <row r="318" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D317" s="5" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="318" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A318" s="1">
         <v>10200093</v>
       </c>
       <c r="B318" s="1" t="s">
-        <v>85</v>
+        <v>106</v>
       </c>
       <c r="C318" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="319" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D318" s="5" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="319" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A319" s="1">
         <v>10200008</v>
       </c>
       <c r="B319" s="1" t="s">
-        <v>85</v>
+        <v>106</v>
       </c>
       <c r="C319" s="1">
         <v>0.8</v>
       </c>
-    </row>
-    <row r="320" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D319" s="5" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="320" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A320" s="1">
         <v>10200005</v>
       </c>
       <c r="B320" s="1" t="s">
-        <v>85</v>
+        <v>106</v>
       </c>
       <c r="C320" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="321" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D320" s="5" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="321" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A321" s="1">
         <v>20000560</v>
       </c>
       <c r="B321" s="1" t="s">
-        <v>85</v>
+        <v>106</v>
       </c>
       <c r="C321" s="1">
         <v>0.5247742001326734</v>
       </c>
-    </row>
-    <row r="322" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D321" s="5" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="322" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A322" s="1">
         <v>20000579</v>
       </c>
       <c r="B322" s="1" t="s">
-        <v>85</v>
+        <v>106</v>
       </c>
       <c r="C322" s="1">
         <v>2.073525813555175E-2</v>
       </c>
-    </row>
-    <row r="323" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D322" s="5" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="323" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A323" s="1">
         <v>31011665</v>
       </c>
       <c r="B323" s="1" t="s">
-        <v>85</v>
+        <v>106</v>
       </c>
       <c r="C323" s="1">
         <v>1.9288666632647853E-3</v>
       </c>
-    </row>
-    <row r="324" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D323" s="5" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="324" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A324" s="1">
         <v>31011666</v>
       </c>
       <c r="B324" s="1" t="s">
-        <v>85</v>
+        <v>106</v>
       </c>
       <c r="C324" s="1">
         <v>8.1592689295039166E-5</v>
       </c>
-    </row>
-    <row r="325" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D324" s="5" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="325" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A325" s="1">
         <v>10200080</v>
       </c>
       <c r="B325" s="1" t="s">
-        <v>85</v>
+        <v>106</v>
       </c>
       <c r="C325" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="326" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D325" s="5" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="326" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A326" s="1">
         <v>10200085</v>
       </c>
       <c r="B326" s="1" t="s">
-        <v>85</v>
+        <v>106</v>
       </c>
       <c r="C326" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="327" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D326" s="5" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="327" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A327" s="1">
         <v>20001578</v>
       </c>
       <c r="B327" s="1" t="s">
-        <v>85</v>
+        <v>106</v>
       </c>
       <c r="C327" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="328" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D327" s="5" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="328" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A328" s="1">
         <v>20000612</v>
       </c>
       <c r="B328" s="1" t="s">
-        <v>85</v>
+        <v>106</v>
       </c>
       <c r="C328" s="1">
         <v>0.02</v>
       </c>
-    </row>
-    <row r="329" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D328" s="5" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="329" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A329" s="1">
         <v>20001668</v>
       </c>
       <c r="B329" s="1" t="s">
-        <v>85</v>
+        <v>106</v>
       </c>
       <c r="C329" s="1">
         <v>0.87829769862734097</v>
       </c>
-    </row>
-    <row r="330" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D329" s="5" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="330" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A330" s="1">
         <v>20001580</v>
       </c>
       <c r="B330" s="1" t="s">
-        <v>85</v>
+        <v>106</v>
       </c>
       <c r="C330" s="1">
         <v>20.2</v>
       </c>
-    </row>
-    <row r="331" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D330" s="5" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="331" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A331" s="1">
         <v>20001688</v>
       </c>
       <c r="B331" s="1" t="s">
-        <v>85</v>
+        <v>106</v>
       </c>
       <c r="C331" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="332" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D331" s="5" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="332" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A332" s="1">
         <v>20000617</v>
       </c>
       <c r="B332" s="1" t="s">
-        <v>85</v>
+        <v>106</v>
       </c>
       <c r="C332" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="333" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D332" s="5" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="333" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A333" s="1">
         <v>10200189</v>
       </c>
       <c r="B333" s="1" t="s">
-        <v>85</v>
+        <v>106</v>
       </c>
       <c r="C333" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="334" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D333" s="5" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="334" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A334" s="1">
         <v>31013555</v>
       </c>
       <c r="B334" s="1" t="s">
-        <v>85</v>
+        <v>106</v>
       </c>
       <c r="C334" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="335" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D334" s="5" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="335" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A335" s="1">
         <v>10200009</v>
       </c>
       <c r="B335" s="1" t="s">
-        <v>85</v>
+        <v>106</v>
       </c>
       <c r="C335" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="336" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D335" s="5" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="336" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A336" s="1">
         <v>10200227</v>
       </c>
       <c r="B336" s="1" t="s">
-        <v>85</v>
+        <v>106</v>
       </c>
       <c r="C336" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="337" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D336" s="5" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="337" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A337" s="1">
         <v>10200045</v>
       </c>
       <c r="B337" s="1" t="s">
-        <v>85</v>
+        <v>106</v>
       </c>
       <c r="C337" s="1">
         <v>2.8371689544318008</v>
       </c>
-    </row>
-    <row r="338" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D337" s="5" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="338" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A338" s="1">
         <v>32004433</v>
       </c>
       <c r="B338" s="1" t="s">
-        <v>85</v>
+        <v>106</v>
       </c>
       <c r="C338" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="339" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D338" s="5" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="339" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A339" s="1">
         <v>32004434</v>
       </c>
       <c r="B339" s="1" t="s">
-        <v>85</v>
+        <v>106</v>
       </c>
       <c r="C339" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="340" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D339" s="5" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="340" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A340" s="1">
         <v>31010981</v>
       </c>
       <c r="B340" s="1" t="s">
-        <v>85</v>
+        <v>106</v>
       </c>
       <c r="C340" s="1">
         <v>0.35413583711792623</v>
       </c>
-    </row>
-    <row r="341" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D340" s="5" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="341" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A341" s="1">
         <v>31010971</v>
       </c>
       <c r="B341" s="1" t="s">
-        <v>85</v>
+        <v>106</v>
       </c>
       <c r="C341" s="1">
         <v>8.9999999999999993E-3</v>
       </c>
-    </row>
-    <row r="342" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D341" s="5" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="342" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A342" s="1">
         <v>31029889</v>
       </c>
       <c r="B342" s="1" t="s">
-        <v>85</v>
+        <v>106</v>
       </c>
       <c r="C342" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="343" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D342" s="5" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="343" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A343" s="1">
         <v>31010973</v>
       </c>
       <c r="B343" s="1" t="s">
-        <v>85</v>
+        <v>106</v>
       </c>
       <c r="C343" s="1">
         <v>5.1028218604888501E-2</v>
       </c>
-    </row>
-    <row r="344" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D343" s="5" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="344" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A344" s="1">
         <v>31010975</v>
       </c>
       <c r="B344" s="1" t="s">
-        <v>85</v>
+        <v>106</v>
       </c>
       <c r="C344" s="1">
         <v>1.7999999999999999E-2</v>
       </c>
-    </row>
-    <row r="345" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D344" s="5" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="345" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A345" s="1">
         <v>31010976</v>
       </c>
       <c r="B345" s="1" t="s">
-        <v>85</v>
+        <v>106</v>
       </c>
       <c r="C345" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="346" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D345" s="5" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="346" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A346" s="1">
         <v>31010977</v>
       </c>
       <c r="B346" s="1" t="s">
-        <v>85</v>
+        <v>106</v>
       </c>
       <c r="C346" s="1">
         <v>3.0616931162933101E-2</v>
       </c>
-    </row>
-    <row r="347" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D346" s="5" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="347" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A347" s="1">
         <v>31029890</v>
       </c>
       <c r="B347" s="1" t="s">
-        <v>85</v>
+        <v>106</v>
       </c>
       <c r="C347" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="348" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D347" s="5" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="348" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A348" s="1">
         <v>10200075</v>
       </c>
       <c r="B348" s="1" t="s">
-        <v>85</v>
+        <v>106</v>
       </c>
       <c r="C348" s="1">
         <v>2</v>
       </c>
-    </row>
-    <row r="349" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D348" s="5" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="349" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A349" s="1">
         <v>10200021</v>
       </c>
       <c r="B349" s="1" t="s">
-        <v>85</v>
+        <v>106</v>
       </c>
       <c r="C349" s="1">
         <v>26</v>
       </c>
-    </row>
-    <row r="350" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D349" s="5" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="350" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A350" s="1">
         <v>10200228</v>
       </c>
       <c r="B350" s="1" t="s">
-        <v>85</v>
+        <v>106</v>
       </c>
       <c r="C350" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="351" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D350" s="5" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="351" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A351" s="1">
         <v>10200023</v>
       </c>
       <c r="B351" s="1" t="s">
-        <v>85</v>
+        <v>106</v>
       </c>
       <c r="C351" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="352" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D351" s="5" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="352" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A352" s="1">
         <v>10200266</v>
       </c>
       <c r="B352" s="1" t="s">
-        <v>85</v>
+        <v>106</v>
       </c>
       <c r="C352" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="353" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D352" s="5" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="353" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A353" s="1">
         <v>10200267</v>
       </c>
       <c r="B353" s="1" t="s">
-        <v>85</v>
+        <v>106</v>
       </c>
       <c r="C353" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="354" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D353" s="5" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="354" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A354" s="1">
         <v>10200265</v>
       </c>
       <c r="B354" s="1" t="s">
-        <v>85</v>
+        <v>106</v>
       </c>
       <c r="C354" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="355" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D354" s="5" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="355" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A355" s="1">
         <v>10200082</v>
       </c>
       <c r="B355" s="1" t="s">
-        <v>85</v>
+        <v>106</v>
       </c>
       <c r="C355" s="1">
         <v>1.2</v>
       </c>
-    </row>
-    <row r="356" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D355" s="5" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="356" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A356" s="1">
         <v>31015345</v>
       </c>
       <c r="B356" s="1" t="s">
-        <v>85</v>
+        <v>106</v>
       </c>
       <c r="C356" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="357" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D356" s="5" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="357" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A357" s="1">
         <v>31010979</v>
       </c>
       <c r="B357" s="1" t="s">
-        <v>85</v>
+        <v>106</v>
       </c>
       <c r="C357" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="358" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D357" s="5" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="358" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A358" s="1">
         <v>31010987</v>
       </c>
       <c r="B358" s="1" t="s">
-        <v>85</v>
+        <v>106</v>
       </c>
       <c r="C358" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="359" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D358" s="5" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="359" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A359" s="1">
         <v>30000527</v>
       </c>
       <c r="B359" s="1" t="s">
-        <v>85</v>
+        <v>106</v>
       </c>
       <c r="C359" s="1">
         <v>0.7</v>
       </c>
-    </row>
-    <row r="360" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D359" s="5" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="360" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A360" s="1">
         <v>30000528</v>
       </c>
       <c r="B360" s="1" t="s">
-        <v>85</v>
+        <v>106</v>
       </c>
       <c r="C360" s="1">
         <v>45</v>
       </c>
-    </row>
-    <row r="361" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D360" s="5" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="361" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A361" s="1">
         <v>30000517</v>
       </c>
       <c r="B361" s="1" t="s">
-        <v>85</v>
+        <v>106</v>
       </c>
       <c r="C361" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="362" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D361" s="5" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="362" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A362" s="1">
         <v>10200012</v>
       </c>
       <c r="B362" s="1" t="s">
-        <v>86</v>
+        <v>107</v>
       </c>
       <c r="C362" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="363" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D362" s="5" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="363" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A363" s="1">
         <v>10200093</v>
       </c>
       <c r="B363" s="1" t="s">
-        <v>86</v>
+        <v>107</v>
       </c>
       <c r="C363" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="364" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D363" s="5" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="364" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A364" s="1">
         <v>10200008</v>
       </c>
       <c r="B364" s="1" t="s">
-        <v>86</v>
+        <v>107</v>
       </c>
       <c r="C364" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="365" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D364" s="5" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="365" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A365" s="1">
         <v>10200005</v>
       </c>
       <c r="B365" s="1" t="s">
-        <v>86</v>
+        <v>107</v>
       </c>
       <c r="C365" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="366" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D365" s="5" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="366" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A366" s="1">
         <v>20000560</v>
       </c>
       <c r="B366" s="1" t="s">
-        <v>86</v>
+        <v>107</v>
       </c>
       <c r="C366" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="367" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D366" s="5" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="367" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A367" s="1">
         <v>20000579</v>
       </c>
       <c r="B367" s="1" t="s">
-        <v>86</v>
+        <v>107</v>
       </c>
       <c r="C367" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="368" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D367" s="5" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="368" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A368" s="1">
         <v>31011665</v>
       </c>
       <c r="B368" s="1" t="s">
-        <v>86</v>
+        <v>107</v>
       </c>
       <c r="C368" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="369" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D368" s="5" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="369" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A369" s="1">
         <v>31011666</v>
       </c>
       <c r="B369" s="1" t="s">
-        <v>86</v>
+        <v>107</v>
       </c>
       <c r="C369" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="370" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D369" s="5" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="370" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A370" s="1">
         <v>10200080</v>
       </c>
       <c r="B370" s="1" t="s">
-        <v>86</v>
+        <v>107</v>
       </c>
       <c r="C370" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="371" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D370" s="5" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="371" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A371" s="1">
         <v>10200085</v>
       </c>
       <c r="B371" s="1" t="s">
-        <v>86</v>
+        <v>107</v>
       </c>
       <c r="C371" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="372" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D371" s="5" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="372" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A372" s="1">
         <v>20001578</v>
       </c>
       <c r="B372" s="1" t="s">
-        <v>86</v>
+        <v>107</v>
       </c>
       <c r="C372" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="373" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D372" s="5" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="373" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A373" s="1">
         <v>20000612</v>
       </c>
       <c r="B373" s="1" t="s">
-        <v>86</v>
+        <v>107</v>
       </c>
       <c r="C373" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="374" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D373" s="5" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="374" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A374" s="1">
         <v>20001668</v>
       </c>
       <c r="B374" s="1" t="s">
-        <v>86</v>
+        <v>107</v>
       </c>
       <c r="C374" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="375" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D374" s="5" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="375" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A375" s="1">
         <v>20001580</v>
       </c>
       <c r="B375" s="1" t="s">
-        <v>86</v>
+        <v>107</v>
       </c>
       <c r="C375" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="376" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D375" s="5" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="376" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A376" s="1">
         <v>20001688</v>
       </c>
       <c r="B376" s="1" t="s">
-        <v>86</v>
+        <v>107</v>
       </c>
       <c r="C376" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="377" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D376" s="5" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="377" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A377" s="1">
         <v>20000617</v>
       </c>
       <c r="B377" s="1" t="s">
-        <v>86</v>
+        <v>107</v>
       </c>
       <c r="C377" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="378" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D377" s="5" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="378" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A378" s="1">
         <v>10200189</v>
       </c>
       <c r="B378" s="1" t="s">
-        <v>86</v>
+        <v>107</v>
       </c>
       <c r="C378" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="379" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D378" s="5" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="379" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A379" s="1">
         <v>31013555</v>
       </c>
       <c r="B379" s="1" t="s">
-        <v>86</v>
+        <v>107</v>
       </c>
       <c r="C379" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="380" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D379" s="5" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="380" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A380" s="1">
         <v>10200009</v>
       </c>
       <c r="B380" s="1" t="s">
-        <v>86</v>
+        <v>107</v>
       </c>
       <c r="C380" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="381" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D380" s="5" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="381" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A381" s="1">
         <v>10200227</v>
       </c>
       <c r="B381" s="1" t="s">
-        <v>86</v>
+        <v>107</v>
       </c>
       <c r="C381" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="382" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D381" s="5" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="382" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A382" s="1">
         <v>10200045</v>
       </c>
       <c r="B382" s="1" t="s">
-        <v>86</v>
+        <v>107</v>
       </c>
       <c r="C382" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="383" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D382" s="5" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="383" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A383" s="1">
         <v>32004433</v>
       </c>
       <c r="B383" s="1" t="s">
-        <v>86</v>
+        <v>107</v>
       </c>
       <c r="C383" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="384" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D383" s="5" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="384" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A384" s="1">
         <v>32004434</v>
       </c>
       <c r="B384" s="1" t="s">
-        <v>86</v>
+        <v>107</v>
       </c>
       <c r="C384" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="385" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D384" s="5" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="385" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A385" s="1">
         <v>31010981</v>
       </c>
       <c r="B385" s="1" t="s">
-        <v>86</v>
+        <v>107</v>
       </c>
       <c r="C385" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="386" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D385" s="5" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="386" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A386" s="1">
         <v>31010971</v>
       </c>
       <c r="B386" s="1" t="s">
-        <v>86</v>
+        <v>107</v>
       </c>
       <c r="C386" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="387" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D386" s="5" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="387" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A387" s="1">
         <v>31029889</v>
       </c>
       <c r="B387" s="1" t="s">
-        <v>86</v>
+        <v>107</v>
       </c>
       <c r="C387" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="388" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D387" s="5" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="388" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A388" s="1">
         <v>31010973</v>
       </c>
       <c r="B388" s="1" t="s">
-        <v>86</v>
+        <v>107</v>
       </c>
       <c r="C388" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="389" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D388" s="5" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="389" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A389" s="1">
         <v>31010975</v>
       </c>
       <c r="B389" s="1" t="s">
-        <v>86</v>
+        <v>107</v>
       </c>
       <c r="C389" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="390" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D389" s="5" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="390" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A390" s="1">
         <v>31010976</v>
       </c>
       <c r="B390" s="1" t="s">
-        <v>86</v>
+        <v>107</v>
       </c>
       <c r="C390" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="391" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D390" s="5" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="391" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A391" s="1">
         <v>31010977</v>
       </c>
       <c r="B391" s="1" t="s">
-        <v>86</v>
+        <v>107</v>
       </c>
       <c r="C391" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="392" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D391" s="5" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="392" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A392" s="1">
         <v>31029890</v>
       </c>
       <c r="B392" s="1" t="s">
-        <v>86</v>
+        <v>107</v>
       </c>
       <c r="C392" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="393" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D392" s="5" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="393" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A393" s="1">
         <v>10200075</v>
       </c>
       <c r="B393" s="1" t="s">
-        <v>86</v>
+        <v>107</v>
       </c>
       <c r="C393" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="394" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D393" s="5" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="394" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A394" s="1">
         <v>10200021</v>
       </c>
       <c r="B394" s="1" t="s">
-        <v>86</v>
+        <v>107</v>
       </c>
       <c r="C394" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="395" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D394" s="5" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="395" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A395" s="1">
         <v>10200228</v>
       </c>
       <c r="B395" s="1" t="s">
-        <v>86</v>
+        <v>107</v>
       </c>
       <c r="C395" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="396" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D395" s="5" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="396" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A396" s="1">
         <v>10200023</v>
       </c>
       <c r="B396" s="1" t="s">
-        <v>86</v>
+        <v>107</v>
       </c>
       <c r="C396" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="397" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D396" s="5" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="397" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A397" s="1">
         <v>10200266</v>
       </c>
       <c r="B397" s="1" t="s">
-        <v>86</v>
+        <v>107</v>
       </c>
       <c r="C397" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="398" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D397" s="5" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="398" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A398" s="1">
         <v>10200267</v>
       </c>
       <c r="B398" s="1" t="s">
-        <v>86</v>
+        <v>107</v>
       </c>
       <c r="C398" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="399" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D398" s="5" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="399" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A399" s="1">
         <v>10200265</v>
       </c>
       <c r="B399" s="1" t="s">
-        <v>86</v>
+        <v>107</v>
       </c>
       <c r="C399" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="400" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D399" s="5" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="400" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A400" s="1">
         <v>10200082</v>
       </c>
       <c r="B400" s="1" t="s">
-        <v>86</v>
+        <v>107</v>
       </c>
       <c r="C400" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="401" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D400" s="5" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="401" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A401" s="1">
         <v>31015345</v>
       </c>
       <c r="B401" s="1" t="s">
-        <v>86</v>
+        <v>107</v>
       </c>
       <c r="C401" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="402" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D401" s="5" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="402" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A402" s="1">
         <v>31010979</v>
       </c>
       <c r="B402" s="1" t="s">
-        <v>86</v>
+        <v>107</v>
       </c>
       <c r="C402" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="403" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D402" s="5" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="403" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A403" s="1">
         <v>31010987</v>
       </c>
       <c r="B403" s="1" t="s">
-        <v>86</v>
+        <v>107</v>
       </c>
       <c r="C403" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="404" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D403" s="5" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="404" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A404" s="1">
         <v>30000527</v>
       </c>
       <c r="B404" s="1" t="s">
-        <v>86</v>
+        <v>107</v>
       </c>
       <c r="C404" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="405" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D404" s="5" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="405" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A405" s="1">
         <v>30000528</v>
       </c>
       <c r="B405" s="1" t="s">
-        <v>86</v>
+        <v>107</v>
       </c>
       <c r="C405" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="406" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D405" s="5" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="406" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A406" s="1">
         <v>30000517</v>
       </c>
       <c r="B406" s="1" t="s">
-        <v>86</v>
+        <v>107</v>
       </c>
       <c r="C406" s="1">
         <v>0</v>
+      </c>
+      <c r="D406" s="5" t="s">
+        <v>99</v>
       </c>
     </row>
   </sheetData>
@@ -6486,25 +7931,25 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5C214E58-CC70-4B54-8DF7-6EF2D2DA5795}">
   <sheetPr codeName="Hoja3"/>
   <dimension ref="A1:C2"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>87</v>
+        <v>108</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>88</v>
+        <v>109</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>89</v>
+        <v>110</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
-        <v>210000</v>
+        <v>2400000</v>
       </c>
       <c r="B2" s="2">
-        <v>0.1416</v>
+        <v>0.13980000000000001</v>
       </c>
       <c r="C2" s="3">
         <v>0.1</v>
@@ -6521,35 +7966,39 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DC9B3BA1-4BF7-412E-9422-B98FA4639657}">
   <sheetPr codeName="Hoja4"/>
-  <dimension ref="A1:E13"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:F13"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="11.28515625" customWidth="1"/>
     <col min="3" max="3" width="20" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="17.42578125" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="14.140625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="17.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>90</v>
+        <v>111</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>91</v>
+        <v>112</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>92</v>
+        <v>113</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+        <v>114</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="B2" s="1">
         <v>200</v>
@@ -6563,10 +8012,13 @@
       <c r="E2" s="1">
         <v>4.03</v>
       </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F2" s="1">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>80</v>
+        <v>101</v>
       </c>
       <c r="B3" s="1">
         <v>60</v>
@@ -6580,10 +8032,13 @@
       <c r="E3" s="1">
         <v>4.03</v>
       </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F3" s="1">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>79</v>
+        <v>100</v>
       </c>
       <c r="B4" s="1">
         <v>200</v>
@@ -6597,10 +8052,13 @@
       <c r="E4" s="1">
         <v>4.03</v>
       </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F4" s="1">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>81</v>
+        <v>102</v>
       </c>
       <c r="B5" s="1">
         <v>80</v>
@@ -6614,10 +8072,13 @@
       <c r="E5" s="1">
         <v>4.03</v>
       </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F5" s="1">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>82</v>
+        <v>103</v>
       </c>
       <c r="B6" s="1">
         <v>140</v>
@@ -6631,10 +8092,13 @@
       <c r="E6" s="1">
         <v>4.03</v>
       </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F6" s="1">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>83</v>
+        <v>104</v>
       </c>
       <c r="B7" s="1">
         <v>200</v>
@@ -6648,10 +8112,13 @@
       <c r="E7" s="1">
         <v>4.03</v>
       </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F7" s="1">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>94</v>
+        <v>115</v>
       </c>
       <c r="B8" s="1">
         <v>90</v>
@@ -6665,10 +8132,13 @@
       <c r="E8" s="1">
         <v>4.03</v>
       </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F8" s="1">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>84</v>
+        <v>105</v>
       </c>
       <c r="B9" s="1">
         <v>130</v>
@@ -6682,10 +8152,13 @@
       <c r="E9" s="1">
         <v>4.03</v>
       </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F9" s="1">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>95</v>
+        <v>116</v>
       </c>
       <c r="B10" s="1">
         <v>130</v>
@@ -6699,10 +8172,13 @@
       <c r="E10" s="1">
         <v>4.03</v>
       </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F10" s="1">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>85</v>
+        <v>106</v>
       </c>
       <c r="B11" s="1">
         <v>130</v>
@@ -6716,10 +8192,13 @@
       <c r="E11" s="1">
         <v>4.03</v>
       </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F11" s="1">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>86</v>
+        <v>107</v>
       </c>
       <c r="B12" s="1">
         <v>200</v>
@@ -6733,10 +8212,13 @@
       <c r="E12" s="1">
         <v>4.03</v>
       </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F12" s="1">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>96</v>
+        <v>117</v>
       </c>
       <c r="B13" s="1">
         <v>80</v>
@@ -6749,6 +8231,9 @@
       </c>
       <c r="E13" s="1">
         <v>4.03</v>
+      </c>
+      <c r="F13" s="1">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
